--- a/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
@@ -1954,7 +1954,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>transition — 6 Sep 3 W9 producer stops kept (built from J-R03)</t>
+          <t>transition — 6 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from J-R03)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>transition — 7 Sep 3 W9 producer stops kept (built from J-R04)</t>
+          <t>transition — 7 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from J-R04)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>transition — 5 Sep 3 W9 producer stops kept (built from J-R06)</t>
+          <t>transition — 5 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from J-R06)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>transition — 2 Sep 3 W9 producer stops kept (built from J-R07)</t>
+          <t>transition — 2 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from J-R07)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>transition — 2 Sep 3 W9 producer stops kept (built from J-R10)</t>
+          <t>transition — 2 Sep 3 W9 producer stops kept on this day (own and neighbouring Sep 3 days; built from J-R10)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="K563" s="3" t="inlineStr">
         <is>
-          <t>Brownstown Twp</t>
+          <t>Brownstown Township</t>
         </is>
       </c>
       <c r="L563" s="4" t="inlineStr">
@@ -38021,7 +38021,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="6" t="n"/>
       <c r="I3" s="7" t="inlineStr">
@@ -38159,7 +38159,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="7" t="inlineStr">
@@ -38195,7 +38195,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="7" t="inlineStr">
@@ -38231,7 +38231,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="7" t="inlineStr">
@@ -38266,7 +38266,9 @@
       <c r="F10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
@@ -38301,7 +38303,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="7" t="inlineStr">
@@ -49246,7 +49248,7 @@
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="K180" s="7" t="inlineStr">
@@ -52947,7 +52949,7 @@
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>Brownstown</t>
+          <t>Brownstown Township</t>
         </is>
       </c>
       <c r="K243" s="7" t="inlineStr">
@@ -57428,7 +57430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -57569,7 +57571,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>8</v>
@@ -57581,7 +57583,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>15</v>
@@ -58456,7 +58458,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Brownstown Twp</t>
+          <t>Brownstown Township</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -58522,7 +58524,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Rd</t>
+          <t>Northville</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
@@ -58548,21 +58550,21 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>J-A09</t>
+          <t>J-A01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Northville</t>
+          <t>Walled Lake</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
@@ -58571,10 +58573,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>0</v>
@@ -58588,18 +58590,18 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Walled Lake</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" s="6" t="n">
         <v>0</v>
       </c>
@@ -58607,21 +58609,21 @@
         <v>0</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>J-A01</t>
+          <t>J-A03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Howell</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
@@ -58631,11 +58633,11 @@
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
       </c>
@@ -58646,39 +58648,6 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>J-A03</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Howell</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>J-A01</t>
         </is>

--- a/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
@@ -2429,7 +2429,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
@@ -2438,17 +2438,17 @@
         <v>0</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Livonia (2) • Garden City (2)</t>
+          <t>Dearborn (3) • Livonia (2)</t>
         </is>
       </c>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219&amp;waypoints=20290%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C21801%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219&amp;waypoints=20290%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>8</v>
@@ -2782,17 +2782,17 @@
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Dearborn (3) • Livonia (2)</t>
+          <t>Livonia (2) • Dearborn Heights (2)</t>
         </is>
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C15100%20S%20PLAZA%20DR%2C%20TAYLOR%2C%20MI%2C%2048180%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C15100%20S%20PLAZA%20DR%2C%20TAYLOR%2C%20MI%2C%2048180%7C21801%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         <v>10</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -2997,17 +2997,17 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Dearborn (3) • Taylor (3)</t>
+          <t>Dearborn (4) • Taylor (2)</t>
         </is>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2865%20West%20Road%2C%20Trenton%2C%20Michigan%2C%2048183&amp;waypoints=3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124%7C9340%20TELEGRAPH%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C12701%20Telegraph%20Rd%2C%20ste%20103%2C%20TAYLOR%2C%20Michigan%2C%2048180%7C11368%20Allen%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192%7C13909%20Pennsylvania%20Road%2C%20Suite%20B%2C%20Riverview%2C%20Michigan%2C%2048193</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2865%20West%20Road%2C%20Trenton%2C%20Michigan%2C%2048183&amp;waypoints=3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124%7C9340%20TELEGRAPH%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C11368%20Allen%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192%7C13909%20Pennsylvania%20Road%2C%20Suite%20B%2C%20Riverview%2C%20Michigan%2C%2048193</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>3</v>
@@ -3083,17 +3083,17 @@
         <v>1</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Southgate (2) • Southfield (2)</t>
+          <t>Taylor (2) • Southgate (2)</t>
         </is>
       </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=36475%205%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%2C%2048154%7C34659%20West%20Michigan%20Avenue%2C%20Wayne%2C%20Michigan%2C%2048184%7C25500%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C19727%20Allen%20Rd%2C%20Ste%2011%2C%20Brownstown%20Twp%2C%20Michigan%2C%2048183%7C13636%20Dix%20Toledo%2C%20Southgate%2C%20MI%2C%20481952432%7C15555%20Northline%20Road%2C%20Southgate%2C%20Michigan%2C%2048195%7C3902%20Monroe%20St%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048125%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=36475%205%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%2C%2048154%7C34659%20West%20Michigan%20Avenue%2C%20Wayne%2C%20Michigan%2C%2048184%7C25500%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C12701%20Telegraph%20Rd%2C%20ste%20103%2C%20TAYLOR%2C%20Michigan%2C%2048180%7C19727%20Allen%20Rd%2C%20Ste%2011%2C%20Brownstown%20Twp%2C%20Michigan%2C%2048183%7C13636%20Dix%20Toledo%2C%20Southgate%2C%20MI%2C%20481952432%7C15555%20Northline%20Road%2C%20Southgate%2C%20Michigan%2C%2048195%7C3902%20Monroe%20St%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048125%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075</t>
         </is>
       </c>
     </row>
@@ -27321,22 +27321,22 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>📝 DOWNRIVER INTERNISTS, PC</t>
+          <t>📝 TENNY INTERNAL MEDICINE, PLLC</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Mar 5</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>0889eef0-5cc1-4032-b658-e4a9c719c997</t>
+          <t>3effe9bc-8576-4eee-ba7e-9bf99eb7d1fa</t>
         </is>
       </c>
       <c r="H391" s="3" t="inlineStr">
@@ -27350,16 +27350,16 @@
         </is>
       </c>
       <c r="J391" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K391" s="3" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L391" s="4" t="inlineStr">
         <is>
-          <t>21801 GODDARD RD, TAYLOR, MI, 48180</t>
+          <t>22361 W VILLAGE DR STE 102, DEARBORN, MI, 48124</t>
         </is>
       </c>
       <c r="M391" s="4" t="n"/>
@@ -27381,12 +27381,12 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>📝 TENNY INTERNAL MEDICINE, PLLC</t>
+          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>3effe9bc-8576-4eee-ba7e-9bf99eb7d1fa</t>
+          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
         </is>
       </c>
       <c r="H392" s="3" t="inlineStr">
@@ -27419,7 +27419,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>22361 W VILLAGE DR STE 102, DEARBORN, MI, 48124</t>
+          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M392" s="4" t="n"/>
@@ -32181,22 +32181,22 @@
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
+          <t>📝 DOWNRIVER INTERNISTS, PC</t>
         </is>
       </c>
       <c r="E472" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Prospect · last check-in Mar 5</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
+          <t>0889eef0-5cc1-4032-b658-e4a9c719c997</t>
         </is>
       </c>
       <c r="H472" s="3" t="inlineStr">
@@ -32210,16 +32210,16 @@
         </is>
       </c>
       <c r="J472" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
+          <t>21801 GODDARD RD, TAYLOR, MI, 48180</t>
         </is>
       </c>
       <c r="M472" s="4" t="n"/>
@@ -34881,12 +34881,12 @@
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>📝 PelHam Primary Care</t>
+          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
         </is>
       </c>
       <c r="E517" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F517" s="3" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
+          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
         </is>
       </c>
       <c r="H517" s="3" t="inlineStr">
@@ -34919,7 +34919,7 @@
       </c>
       <c r="L517" s="4" t="inlineStr">
         <is>
-          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
+          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M517" s="4" t="n"/>
@@ -34941,22 +34941,22 @@
       </c>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT FAMILY MEDICINE CLINIC TAYLOR</t>
+          <t>📝 PelHam Primary Care</t>
         </is>
       </c>
       <c r="E518" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Apr 8</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F518" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>ca75c2bf-f7ff-43df-9399-5f78f3147237</t>
+          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
         </is>
       </c>
       <c r="H518" s="3" t="inlineStr">
@@ -34970,16 +34970,16 @@
         </is>
       </c>
       <c r="J518" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>9340 TELEGRAPH RD, TAYLOR, MI, 48180</t>
+          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
         </is>
       </c>
       <c r="M518" s="4" t="n"/>
@@ -35001,7 +35001,7 @@
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>📝 PARK PLACE FAMILY PRACTICE AND INTERNAL MEDICINE</t>
+          <t>📝 BEAUMONT FAMILY MEDICINE CLINIC TAYLOR</t>
         </is>
       </c>
       <c r="E519" s="4" t="inlineStr">
@@ -35016,12 +35016,12 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>f8f13fd9-1135-4385-b6ba-7542d202b63a</t>
+          <t>ca75c2bf-f7ff-43df-9399-5f78f3147237</t>
         </is>
       </c>
       <c r="H519" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I519" s="3" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="L519" s="4" t="inlineStr">
         <is>
-          <t>12701 Telegraph Rd, ste 103, TAYLOR, Michigan, 48180</t>
+          <t>9340 TELEGRAPH RD, TAYLOR, MI, 48180</t>
         </is>
       </c>
       <c r="M519" s="4" t="n"/>
@@ -36141,12 +36141,12 @@
       </c>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>📝 AMINI HEALTHCARE, PLLC</t>
+          <t>📝 PARK PLACE FAMILY PRACTICE AND INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="E538" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in May 29</t>
+          <t>Prospect · last check-in Apr 8</t>
         </is>
       </c>
       <c r="F538" s="3" t="inlineStr">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>51be485c-bce1-4997-8e82-1463313f4617</t>
+          <t>f8f13fd9-1135-4385-b6ba-7542d202b63a</t>
         </is>
       </c>
       <c r="H538" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I538" s="3" t="inlineStr">
@@ -36174,12 +36174,12 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>Brownstown Township</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>19727 Allen Rd, Ste 11, Brownstown Twp, Michigan, 48183</t>
+          <t>12701 Telegraph Rd, ste 103, TAYLOR, Michigan, 48180</t>
         </is>
       </c>
       <c r="M538" s="4" t="n"/>
@@ -36201,27 +36201,27 @@
       </c>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>📝 City Medical - Southgate</t>
+          <t>📝 AMINI HEALTHCARE, PLLC</t>
         </is>
       </c>
       <c r="E539" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 21</t>
+          <t>Prospect · last check-in May 29</t>
         </is>
       </c>
       <c r="F539" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>1326021262</t>
+          <t>51be485c-bce1-4997-8e82-1463313f4617</t>
         </is>
       </c>
       <c r="H539" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I539" s="3" t="inlineStr">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="K539" s="3" t="inlineStr">
         <is>
-          <t>Southgate</t>
+          <t>Brownstown Township</t>
         </is>
       </c>
       <c r="L539" s="4" t="inlineStr">
         <is>
-          <t>13636 Dix Toledo, Southgate, MI, 481952432</t>
+          <t>19727 Allen Rd, Ste 11, Brownstown Twp, Michigan, 48183</t>
         </is>
       </c>
       <c r="M539" s="4" t="n"/>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>📝 PEDIATRIC AND ADOLESCENT CENTER</t>
+          <t>📝 City Medical - Southgate</t>
         </is>
       </c>
       <c r="E540" s="4" t="inlineStr">
@@ -36276,12 +36276,12 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>31fe13d8-1060-4c98-bf75-61f09e803121</t>
+          <t>1326021262</t>
         </is>
       </c>
       <c r="H540" s="3" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I540" s="3" t="inlineStr">
@@ -36299,7 +36299,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>15555 Northline Road, Southgate, Michigan, 48195</t>
+          <t>13636 Dix Toledo, Southgate, MI, 481952432</t>
         </is>
       </c>
       <c r="M540" s="4" t="n"/>
@@ -36321,27 +36321,27 @@
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>📝 Primary Care Center</t>
+          <t>📝 PEDIATRIC AND ADOLESCENT CENTER</t>
         </is>
       </c>
       <c r="E541" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 17</t>
+          <t>Tier 2 ortho · last check-in Sep 21</t>
         </is>
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>814ed74d-d989-4209-bc8c-83f8248094b6</t>
+          <t>31fe13d8-1060-4c98-bf75-61f09e803121</t>
         </is>
       </c>
       <c r="H541" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I541" s="3" t="inlineStr">
@@ -36354,12 +36354,12 @@
       </c>
       <c r="K541" s="3" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Southgate</t>
         </is>
       </c>
       <c r="L541" s="4" t="inlineStr">
         <is>
-          <t>3902 Monroe St, Dearborn Heights, Michigan, 48125</t>
+          <t>15555 Northline Road, Southgate, Michigan, 48195</t>
         </is>
       </c>
       <c r="M541" s="4" t="n"/>
@@ -36381,22 +36381,22 @@
       </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
+          <t>📝 Primary Care Center</t>
         </is>
       </c>
       <c r="E542" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Prospect · last check-in Jun 17</t>
         </is>
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
+          <t>814ed74d-d989-4209-bc8c-83f8248094b6</t>
         </is>
       </c>
       <c r="H542" s="3" t="inlineStr">
@@ -36410,16 +36410,16 @@
         </is>
       </c>
       <c r="J542" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
+          <t>3902 Monroe St, Dearborn Heights, Michigan, 48125</t>
         </is>
       </c>
       <c r="M542" s="4" t="n"/>
@@ -65206,7 +65206,7 @@
         <v>50</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>10</v>
@@ -65215,7 +65215,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -65231,7 +65231,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>22</v>
@@ -65240,7 +65240,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -65256,7 +65256,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>7</v>
@@ -65265,7 +65265,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -65281,7 +65281,7 @@
         <v>47</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>23</v>
@@ -65290,7 +65290,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">

--- a/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Jasmine.xlsx
@@ -2386,7 +2386,7 @@
         <v>10</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=24430%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127&amp;waypoints=55840%20Grand%20River%20Ave%20ste%20300%2C%20New%20Hudson%2C%20Michigan%2C%2048165%7C26850%20PROVIDENCE%20PKWY%20STE%20420%2C%20NOVI%2C%20Michigan%2C%2048374%7C620%20N%20Pontiac%20Trail%2C%20Walled%20Lake%2C%20MI%2048390%7C20311%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152%7C20206%20Farmington%20Rd%2C%20Livonia%2C%20MI%2C%2048152%7C19000%20St%20Joe%27s%20Pkwy%2C%20Livonia%2C%20Michigan%2C%2048152%7C36650%20Five%20Mile%20Rd%20suite%20106%2C%20Livonia%2C%20Michigan%2C%2048154%7C15140%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C15130%20Levan%20Rd%2C%20Livonia%2C%20MI%2C%2048154</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=55840%20Grand%20River%20Ave%20ste%20300%2C%20New%20Hudson%2C%20Michigan%2C%2048165%7C26850%20PROVIDENCE%20PKWY%20STE%20420%2C%20NOVI%2C%20Michigan%2C%2048374%7C620%20N%20Pontiac%20Trail%2C%20Walled%20Lake%2C%20MI%2048390%7C19000%20St%20Joe%27s%20Pkwy%2C%20Livonia%2C%20Michigan%2C%2048152%7C36650%20Five%20Mile%20Rd%20suite%20106%2C%20Livonia%2C%20Michigan%2C%2048154%7C15140%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C15130%20Levan%20Rd%2C%20Livonia%2C%20MI%2C%2048154%7C20206%20Farmington%20Rd%2C%20Livonia%2C%20MI%2C%2048152%7C20311%20Farmington%20Road%2C%20Livonia%2C%20Michigan%2C%2048152</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
         <v>10</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>4</v>
@@ -2696,17 +2696,17 @@
         <v>2</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Southfield (5) • Livonia (3)</t>
+          <t>Southfield (4) • Livonia (3)</t>
         </is>
       </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6840%20Greenfield%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=20321%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C20331%20FARMINGTON%20RD%20STE%20103%2C%20LIVONIA%2C%20MI%2C%2048152%7C15160%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034%7C21816%20w%2011%20mile%20rd%2C%20Southfield%2C%20Michigan%2C%2048076%7C23832%20SOUTHFIELD%20RD%20STE%201%2C%20SOUTHFIELD%2C%20Michigan%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075%7C22250%20PROVIDENCE%20DR%20STE%20301%2C%20SOUTHFIELD%2C%20Michigan%2C%2048075%7C14650%20W%20WARREN%20AVE%20STE%20150%2C%20DEARBORN%2C%20Michigan%2C%2048126</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=6840%20Greenfield%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=20321%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C20331%20FARMINGTON%20RD%20STE%20103%2C%20LIVONIA%2C%20MI%2C%2048152%7C15160%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C21816%20w%2011%20mile%20rd%2C%20Southfield%2C%20Michigan%2C%2048076%7C23832%20SOUTHFIELD%20RD%20STE%201%2C%20SOUTHFIELD%2C%20Michigan%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075%7C22250%20PROVIDENCE%20DR%20STE%20301%2C%20SOUTHFIELD%2C%20Michigan%2C%2048075%7C14650%20W%20WARREN%20AVE%20STE%20150%2C%20DEARBORN%2C%20Michigan%2C%2048126%7C14716%20W%20WARREN%20AVE%2C%20DEARBORN%2C%20Michigan%2C%2048126</t>
         </is>
       </c>
     </row>
@@ -2786,13 +2786,13 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Livonia (2) • Dearborn Heights (2)</t>
+          <t>Dearborn Heights (3) • Livonia (2)</t>
         </is>
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C15100%20S%20PLAZA%20DR%2C%20TAYLOR%2C%20MI%2C%2048180%7C21801%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C24430%20Ford%20Road%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C21801%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219&amp;waypoints=29370%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C9216%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C6%20parklane%20Blvd%2C%20Suite%20436%2C%20DEARBORN%2C%20Michigan%2C%2048126%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219&amp;waypoints=29370%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C9216%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C15100%20S%20PLAZA%20DR%2C%20TAYLOR%2C%20MI%2C%2048180%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227</t>
         </is>
       </c>
     </row>
@@ -3001,13 +3001,13 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Dearborn (4) • Taylor (2)</t>
+          <t>Dearborn (5) • Taylor (1)</t>
         </is>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2865%20West%20Road%2C%20Trenton%2C%20Michigan%2C%2048183&amp;waypoints=3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124%7C9340%20TELEGRAPH%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C11368%20Allen%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192%7C13909%20Pennsylvania%20Road%2C%20Suite%20B%2C%20Riverview%2C%20Michigan%2C%2048193</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2865%20West%20Road%2C%20Trenton%2C%20Michigan%2C%2048183&amp;waypoints=3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C6%20parklane%20Blvd%2C%20Suite%20436%2C%20DEARBORN%2C%20Michigan%2C%2048126%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124%7C11368%20Allen%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192%7C13909%20Pennsylvania%20Road%2C%20Suite%20B%2C%20Riverview%2C%20Michigan%2C%2048193</t>
         </is>
       </c>
     </row>
@@ -3044,13 +3044,13 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Eastpointe (4) • Dearborn (3)</t>
+          <t>Eastpointe (4) • Detroit (2)</t>
         </is>
       </c>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=1921%208%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048091&amp;waypoints=14716%20W%20WARREN%20AVE%2C%20DEARBORN%2C%20Michigan%2C%2048126%7C10066%20Dix%2C%20Dearborn%2C%20Michigan%2C%2048120%7C9925%20Dix%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048120%7C4201%20St%20Antoine%2C%20Detroit%2C%20Michigan%2C%2048201%7C12871%20East%20Jefferson%20Avenue%2C%20Detroit%2C%20Michigan%2C%2048215%7C21811%20Kelly%20Rd%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C22850%20Kelly%20Rd%2C%20ste%201%2C%20Eastpointe%2C%20MI%2C%2048021%7C19070%20East%2010%20Mile%20Road%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C24901%20Kelly%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=10066%20Dix%2C%20Dearborn%2C%20Michigan%2C%2048120&amp;waypoints=23832%20Southfield%20Road%2C%20Southfield%2C%20Michigan%2C%2048075%7C1921%208%20Mile%20Road%2C%20Warren%2C%20Michigan%2C%2048091%7C24901%20Kelly%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021%7C19070%20East%2010%20Mile%20Road%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C22850%20Kelly%20Rd%2C%20ste%201%2C%20Eastpointe%2C%20MI%2C%2048021%7C21811%20Kelly%20Rd%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C12871%20East%20Jefferson%20Avenue%2C%20Detroit%2C%20Michigan%2C%2048215%7C4201%20St%20Antoine%2C%20Detroit%2C%20Michigan%2C%2048201%7C9925%20Dix%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048120</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=36475%205%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%2C%2048154%7C34659%20West%20Michigan%20Avenue%2C%20Wayne%2C%20Michigan%2C%2048184%7C25500%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C12701%20Telegraph%20Rd%2C%20ste%20103%2C%20TAYLOR%2C%20Michigan%2C%2048180%7C19727%20Allen%20Rd%2C%20Ste%2011%2C%20Brownstown%20Twp%2C%20Michigan%2C%2048183%7C13636%20Dix%20Toledo%2C%20Southgate%2C%20MI%2C%20481952432%7C15555%20Northline%20Road%2C%20Southgate%2C%20Michigan%2C%2048195%7C3902%20Monroe%20St%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048125%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=27207%20Lahser%20Rd%2C%20Southfield%2C%20Michigan%2C%2048034&amp;waypoints=36475%205%20MILE%20RD%2C%20LIVONIA%2C%20Michigan%2C%2048154%7C34659%20West%20Michigan%20Avenue%2C%20Wayne%2C%20Michigan%2C%2048184%7C12701%20Telegraph%20Rd%2C%20ste%20103%2C%20TAYLOR%2C%20Michigan%2C%2048180%7C19727%20Allen%20Rd%2C%20Ste%2011%2C%20Brownstown%20Twp%2C%20Michigan%2C%2048183%7C13636%20Dix%20Toledo%2C%20Southgate%2C%20MI%2C%20481952432%7C15555%20Northline%20Road%2C%20Southgate%2C%20Michigan%2C%2048195%7C9340%20TELEGRAPH%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C3902%20Monroe%20St%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048125%7C22250%20Providence%20Drive%2C%20ste%20401%2C%20Southfield%2C%20Michigan%2C%2048075</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>0</v>
@@ -3212,21 +3212,17 @@
         <v>1</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Taylor (4) • Trenton (2)</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>SHORT DAY (7 stops): nothing else due within reach — finish early or add nearby not-yet-due prospects</t>
-        </is>
-      </c>
+          <t>Taylor (5) • Trenton (2)</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="n"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2901%20West%20Rd%2C%20Trenton%2C%20MI%2048183&amp;waypoints=23300%20ECORSE%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C23234%20Ecorse%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C22021%20ECORSE%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C25404%20Goddard%20Road%2C%20Taylor%2C%20MI%2C%2048180%7C19135%20ALLEN%20RD%20STE%20106%2C%20BROWNSTOWN%2C%20MI%2C%2048183%7C1570%20Kingsway%20Ct%20suite%201%2C%20Trenton%2C%20Michigan%2C%2048183</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=2901%20West%20Rd%2C%20Trenton%2C%20MI%2048183&amp;waypoints=23300%20ECORSE%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C23234%20Ecorse%20Road%2C%20Taylor%2C%20Michigan%2C%2048180%7C22021%20ECORSE%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C25404%20Goddard%20Road%2C%20Taylor%2C%20MI%2C%2048180%7C25500%20GODDARD%20RD%2C%20TAYLOR%2C%20MI%2C%2048180%7C19135%20ALLEN%20RD%20STE%20106%2C%20BROWNSTOWN%2C%20MI%2C%2048183%7C1570%20Kingsway%20Ct%20suite%201%2C%20Trenton%2C%20Michigan%2C%2048183</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3308,7 @@
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=13840%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126&amp;waypoints=37595%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C37595%207%20mile%20rd%2C%20ste%20210%2C%20LIVONIA%2C%20Michigan%2C%2048152%7C20321%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=4700%20Schaefer%20Rd%2C%20Suite%20240%2C%20Dearborn%2C%20MI%2C%20481263698&amp;waypoints=37595%20W%20Seven%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048152%7C37595%207%20mile%20rd%2C%20ste%20210%2C%20LIVONIA%2C%20Michigan%2C%2048152%7C20321%20FARMINGTON%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C28479%207%20MILE%20RD%2C%20LIVONIA%2C%20MI%2C%2048152%7C29150%20FORD%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C27250%20Cherry%20Hill%20Road%2C%20Dearborn%20Heights%2C%20MI%2048127%7C25350%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C22361%20W%20VILLAGE%20DR%20STE%20102%2C%20DEARBORN%2C%20MI%2C%2048124%7C3815%20Pelham%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3351,7 @@
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=23832%20Southfield%20Road%2C%20Southfield%2C%20Michigan%2C%2048075&amp;waypoints=29370%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C9216%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227%7C20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20001%20West%20Seven%20Mile%20Road%2C%20Detroit%2C%20Michigan%2C%2048219&amp;waypoints=29370%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C28701%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C9216%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C5823%20MIDDLEBELT%20RD%2C%20GARDEN%20CITY%2C%20MI%2C%2048135%7C29454%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C27155%20CHERRY%20HILL%20RD%2C%20INKSTER%2C%20MI%2C%2048141%7C23870%20Michigan%20Ave%2C%20Dearborn%2C%20MI%20nan%7C5280%20Oakman%20Blvd%2C%20Dearborn%2C%20Michigan%2C%2048126%7C16226%20Grand%20River%20Ave%2C%20Detroit%2C%20Michigan%2C%2048227</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3394,7 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20331%20FARMINGTON%20RD%20STE%20103%2C%20LIVONIA%2C%20MI%2C%2048152&amp;waypoints=7330%20N%20CANTON%20CENTER%20RD%20STE%20111%2C%20CANTON%2C%20MI%2C%2048187%7C43050%20Ford%20Road%20Ste%20150%2C%20Canton%2C%20Michigan%2C%2048187%7C2050%20North%20Haggerty%20Road%2C%20CANTON%2C%20Michigan%2C%2048187%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C5280%20Oakman%20Blvd%2C%20Dearborn%2C%20Michigan%2C%2048126%7C14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C15160%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C15130%20Levan%20Rd%2C%20Livonia%2C%20MI%2C%2048154</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=20331%20FARMINGTON%20RD%20STE%20103%2C%20LIVONIA%2C%20MI%2C%2048152&amp;waypoints=7330%20N%20CANTON%20CENTER%20RD%20STE%20111%2C%20CANTON%2C%20MI%2C%2048187%7C43050%20Ford%20Road%20Ste%20150%2C%20Canton%2C%20Michigan%2C%2048187%7C2050%20North%20Haggerty%20Road%2C%20CANTON%2C%20Michigan%2C%2048187%7C4020%20Venoy%20Rd%20suite%20400%2C%20Wayne%2C%20Michigan%2C%2048184%7C3133%20South%20Telegraph%20Road%2C%20Dearborn%2C%20Michigan%2C%2048124%7C13840%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126%7C14555%20Levan%20Rd%20suite%20308%2C%20Livonia%2C%20Michigan%2C%2048154%7C15160%20Levan%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C15130%20Levan%20Rd%2C%20Livonia%2C%20MI%2C%2048154</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3523,7 @@
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=4700%20Schaefer%20Rd%2C%20Suite%20240%2C%20Dearborn%2C%20MI%2C%20481263698&amp;waypoints=33464%20Schoenherr%20Road%2C%20Sterling%20Heights%2C%20MI%2048312%7C17000%20E%2010%20Mile%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021%7C24901%20Kelly%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021%7C19070%20East%2010%20Mile%20Road%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C18161%20E%208%20Mile%20Rd%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C12871%20East%20Jefferson%20Avenue%2C%20Detroit%2C%20Michigan%2C%2048215%7C4201%20St%20Antoine%2C%20Detroit%2C%20Michigan%2C%2048201%7C4160%20John%20R%20St%2C%20Ste%20522%2C%20Detroit%2C%20MI%2048201%7C9550%20Dix%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048120</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=9550%20Dix%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048120&amp;waypoints=33464%20Schoenherr%20Road%2C%20Sterling%20Heights%2C%20MI%2048312%7C17000%20E%2010%20Mile%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021%7C24901%20Kelly%20Rd%2C%20Eastpointe%2C%20MI%2C%2048021%7C19070%20East%2010%20Mile%20Road%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C18161%20E%208%20Mile%20Rd%2C%20Eastpointe%2C%20Michigan%2C%2048021%7C12871%20East%20Jefferson%20Avenue%2C%20Detroit%2C%20Michigan%2C%2048215%7C4201%20St%20Antoine%2C%20Detroit%2C%20Michigan%2C%2048201%7C4160%20John%20R%20St%2C%20Ste%20522%2C%20Detroit%2C%20MI%2048201%7C7542%20Wyoming%20Avenue%2C%20Dearborn%2C%20Michigan%2C%2048126</t>
         </is>
       </c>
     </row>
@@ -3564,13 +3560,13 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Livonia (4) • Garden City (2)</t>
+          <t>Livonia (3) • Dearborn (3)</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=5220%20OAKMAN%20BLVD%2C%20DEARBORN%2C%20Michigan%2C%2048126&amp;waypoints=29531%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C11027%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C11502%20Middlebelt%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C9555%20Middlebelt%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C27144%20Joy%20Rd%2C%20Redford%2C%20MI%2C%2048239%7C24950%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C6255%20Inkster%20Rd%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C28511%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C24100%20Oxford%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=5220%20OAKMAN%20BLVD%2C%20DEARBORN%2C%20Michigan%2C%2048126&amp;waypoints=29531%20Plymouth%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C11502%20Middlebelt%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C9555%20Middlebelt%20Road%2C%20Livonia%2C%20Michigan%2C%2048150%7C27144%20Joy%20Rd%2C%20Redford%2C%20MI%2C%2048239%7C24950%20West%20Warren%20Street%2C%20Dearborn%20Heights%2C%20Michigan%2C%2048127%7C6255%20Inkster%20Rd%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C28511%20Ford%20Road%2C%20Garden%20City%2C%20Michigan%2C%2048135%7C24604%20MICHIGAN%20AVE%20STE%20100%2C%20DEARBORN%2C%20MI%2C%2048124%7C24100%20Oxford%20Street%2C%20Dearborn%2C%20Michigan%2C%2048124</t>
         </is>
       </c>
     </row>
@@ -3607,13 +3603,13 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Dearborn (6) • Livonia (2)</t>
+          <t>Dearborn (5) • Livonia (3)</t>
         </is>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195&amp;waypoints=28404%20Five%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C29539%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126%7C13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126%7C7526%20WYOMING%20ST%20STE%202%2C%20DEARBORN%2C%20MI%2C%2048126%7C7542%20Wyoming%20Avenue%2C%20Dearborn%2C%20Michigan%2C%2048126%7C8740%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;travelmode=driving&amp;dir_action=navigate&amp;destination=15450%20Northline%20Road%2C%20Southgate%2C%20MI%2048195&amp;waypoints=28404%20Five%20Mile%20Rd%2C%20Livonia%2C%20Michigan%2C%2048154%7C29539%20Plymouth%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C11027%20Middlebelt%20Rd%2C%20Livonia%2C%20Michigan%2C%2048150%7C17000%20Hubbard%20Dr%2C%20Dearborn%2C%20Michigan%2C%2048126%7C5245%20Schaefer%20Rd%2C%20Dearborn%2C%20Michigan%2C%2048126%7C13244%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126%7C7526%20WYOMING%20ST%20STE%202%2C%20DEARBORN%2C%20MI%2C%2048126%7C8740%20W%20Warren%20Ave%2C%20Dearborn%2C%20Michigan%2C%2048126%7C2300%20Biddle%20Avenue%2C%20Wyandotte%2C%20Michigan%2C%2048192</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N671"/>
+  <dimension ref="A1:N672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -26541,12 +26537,12 @@
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>📝 NORLIVO INTERNAL MEDICINE</t>
+          <t>Trinity IHA Orthopedics - Schoolcraft</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr">
@@ -26556,7 +26552,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>74262c96-dd4b-4b92-acd7-c43ebba4c04f</t>
+          <t>e5c5b135-ecad-42bb-bbbc-011dd2c4a225</t>
         </is>
       </c>
       <c r="H378" s="3" t="inlineStr">
@@ -26570,7 +26566,7 @@
         </is>
       </c>
       <c r="J378" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
@@ -26579,7 +26575,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>20311 Farmington Road, Livonia, Michigan, 48152</t>
+          <t>19000 St Joe's Pkwy, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M378" s="4" t="n"/>
@@ -26601,12 +26597,12 @@
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>📝 Freedom Medical Clinic (Trinity)</t>
+          <t>📝 Lakes Urgent Care - Livonia</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F379" s="3" t="inlineStr">
@@ -26616,12 +26612,12 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>e0d8c74a-31fe-4da6-9aa4-6a2357088b6a</t>
+          <t>73107e68-fc7f-46d0-bef4-ee26e9dc0099</t>
         </is>
       </c>
       <c r="H379" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I379" s="3" t="inlineStr">
@@ -26639,7 +26635,7 @@
       </c>
       <c r="L379" s="4" t="inlineStr">
         <is>
-          <t>20206 Farmington Rd, Livonia, MI, 48152</t>
+          <t>36650 Five Mile Rd suite 106, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M379" s="4" t="n"/>
@@ -26661,12 +26657,12 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Trinity IHA Orthopedics - Schoolcraft</t>
+          <t>📝 Comprehensive Healthcare Associates and Prevention Medicine</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
@@ -26676,12 +26672,12 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>e5c5b135-ecad-42bb-bbbc-011dd2c4a225</t>
+          <t>c7781046-a235-49fa-ac8e-4b8d6354c618</t>
         </is>
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr">
@@ -26690,7 +26686,7 @@
         </is>
       </c>
       <c r="J380" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
@@ -26699,7 +26695,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>19000 St Joe's Pkwy, Livonia, Michigan, 48152</t>
+          <t>15140 Levan Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M380" s="4" t="n"/>
@@ -26721,12 +26717,12 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>📝 Lakes Urgent Care - Livonia</t>
+          <t>📝 Levan Internists</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F381" s="3" t="inlineStr">
@@ -26736,12 +26732,12 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>73107e68-fc7f-46d0-bef4-ee26e9dc0099</t>
+          <t>1972528818</t>
         </is>
       </c>
       <c r="H381" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I381" s="3" t="inlineStr">
@@ -26750,7 +26746,7 @@
         </is>
       </c>
       <c r="J381" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
@@ -26759,7 +26755,7 @@
       </c>
       <c r="L381" s="4" t="inlineStr">
         <is>
-          <t>36650 Five Mile Rd suite 106, Livonia, Michigan, 48154</t>
+          <t>15130 Levan Rd, Livonia, MI, 48154</t>
         </is>
       </c>
       <c r="M381" s="4" t="n"/>
@@ -26781,12 +26777,12 @@
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>📝 Comprehensive Healthcare Associates and Prevention Medicine</t>
+          <t>📝 Freedom Medical Clinic (Trinity)</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr">
@@ -26796,7 +26792,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>c7781046-a235-49fa-ac8e-4b8d6354c618</t>
+          <t>e0d8c74a-31fe-4da6-9aa4-6a2357088b6a</t>
         </is>
       </c>
       <c r="H382" s="3" t="inlineStr">
@@ -26810,7 +26806,7 @@
         </is>
       </c>
       <c r="J382" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
@@ -26819,7 +26815,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>15140 Levan Rd, Livonia, Michigan, 48154</t>
+          <t>20206 Farmington Rd, Livonia, MI, 48152</t>
         </is>
       </c>
       <c r="M382" s="4" t="n"/>
@@ -26841,12 +26837,12 @@
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>📝 Levan Internists</t>
+          <t>📝 NORLIVO INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F383" s="3" t="inlineStr">
@@ -26856,12 +26852,12 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>1972528818</t>
+          <t>74262c96-dd4b-4b92-acd7-c43ebba4c04f</t>
         </is>
       </c>
       <c r="H383" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I383" s="3" t="inlineStr">
@@ -26870,7 +26866,7 @@
         </is>
       </c>
       <c r="J383" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K383" s="3" t="inlineStr">
         <is>
@@ -26879,7 +26875,7 @@
       </c>
       <c r="L383" s="4" t="inlineStr">
         <is>
-          <t>15130 Levan Rd, Livonia, MI, 48154</t>
+          <t>20311 Farmington Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M383" s="4" t="n"/>
@@ -26901,22 +26897,22 @@
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>📝 MICHIGAN INTERVENTIONAL PAIN CENTER (this is an ASC)</t>
+          <t>📝 Roberts Orthopedic Services</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jan 26</t>
+          <t>Tier 1 producer · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>d1235093-a65c-465a-ace2-cffd3d4ad232</t>
+          <t>680822f2-58d4-4f67-b09b-01ccd6f95892</t>
         </is>
       </c>
       <c r="H384" s="3" t="inlineStr">
@@ -26930,16 +26926,16 @@
         </is>
       </c>
       <c r="J384" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>24430 Ford Road, Dearborn Heights, Michigan, 48127</t>
+          <t>27207 Lahser Rd, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M384" s="4" t="n"/>
@@ -30741,22 +30737,22 @@
       </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>📝 Roberts Orthopedic Services</t>
+          <t>📝 DEDICATED SENIOR MEDICAL CENTER - Southfield</t>
         </is>
       </c>
       <c r="E448" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 8</t>
+          <t>Tier 3 · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>680822f2-58d4-4f67-b09b-01ccd6f95892</t>
+          <t>12deaf83-0f5e-4bd5-bf07-a4026935ffd1</t>
         </is>
       </c>
       <c r="H448" s="3" t="inlineStr">
@@ -30770,7 +30766,7 @@
         </is>
       </c>
       <c r="J448" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
@@ -30779,7 +30775,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>27207 Lahser Rd, Southfield, Michigan, 48034</t>
+          <t>21816 w 11 mile rd, Southfield, Michigan, 48076</t>
         </is>
       </c>
       <c r="M448" s="4" t="n"/>
@@ -30801,7 +30797,7 @@
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>📝 DEDICATED SENIOR MEDICAL CENTER - Southfield</t>
+          <t>📝 SOUTHFIELD URGENT CARE</t>
         </is>
       </c>
       <c r="E449" s="4" t="inlineStr">
@@ -30816,12 +30812,12 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>12deaf83-0f5e-4bd5-bf07-a4026935ffd1</t>
+          <t>f8db03fe-3188-4a31-b4ee-6010086c7552</t>
         </is>
       </c>
       <c r="H449" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I449" s="3" t="inlineStr">
@@ -30839,7 +30835,7 @@
       </c>
       <c r="L449" s="4" t="inlineStr">
         <is>
-          <t>21816 w 11 mile rd, Southfield, Michigan, 48076</t>
+          <t>23832 SOUTHFIELD RD STE 1, SOUTHFIELD, Michigan</t>
         </is>
       </c>
       <c r="M449" s="4" t="n"/>
@@ -30861,27 +30857,27 @@
       </c>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>📝 SOUTHFIELD URGENT CARE</t>
+          <t>📝 Core Institute/Henry Ford Motor City Orthopedics &amp; PT- Southfield</t>
         </is>
       </c>
       <c r="E450" s="4" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>f8db03fe-3188-4a31-b4ee-6010086c7552</t>
+          <t>b2290856-de23-4322-aabc-b2436529feac</t>
         </is>
       </c>
       <c r="H450" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I450" s="3" t="inlineStr">
@@ -30890,7 +30886,7 @@
         </is>
       </c>
       <c r="J450" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
@@ -30899,7 +30895,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>23832 SOUTHFIELD RD STE 1, SOUTHFIELD, Michigan</t>
+          <t>22250 Providence Drive, ste 401, Southfield, Michigan, 48075</t>
         </is>
       </c>
       <c r="M450" s="4" t="n"/>
@@ -30921,27 +30917,27 @@
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>📝 Core Institute/Henry Ford Motor City Orthopedics &amp; PT- Southfield</t>
+          <t>📝 ACADEMIC INTERNAL MEDICINE SPECIALISTS</t>
         </is>
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 2 ortho · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>b2290856-de23-4322-aabc-b2436529feac</t>
+          <t>24230075-46f5-44cf-bd8f-deb5f276aa99</t>
         </is>
       </c>
       <c r="H451" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I451" s="3" t="inlineStr">
@@ -30950,7 +30946,7 @@
         </is>
       </c>
       <c r="J451" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K451" s="3" t="inlineStr">
         <is>
@@ -30959,7 +30955,7 @@
       </c>
       <c r="L451" s="4" t="inlineStr">
         <is>
-          <t>22250 Providence Drive, ste 401, Southfield, Michigan, 48075</t>
+          <t>22250 PROVIDENCE DR STE 301, SOUTHFIELD, Michigan, 48075</t>
         </is>
       </c>
       <c r="M451" s="4" t="n"/>
@@ -30981,22 +30977,22 @@
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>📝 ACADEMIC INTERNAL MEDICINE SPECIALISTS</t>
+          <t>📝 EAST DEARBORN MEDICAL CLINIC, PC (Medicaid)</t>
         </is>
       </c>
       <c r="E452" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 10</t>
+          <t>Prospect · last check-in Jun 1</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>24230075-46f5-44cf-bd8f-deb5f276aa99</t>
+          <t>e73a93c2-41c4-488a-8474-89698cf619bb</t>
         </is>
       </c>
       <c r="H452" s="3" t="inlineStr">
@@ -31014,12 +31010,12 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>22250 PROVIDENCE DR STE 301, SOUTHFIELD, Michigan, 48075</t>
+          <t>14650 W WARREN AVE STE 150, DEARBORN, Michigan, 48126</t>
         </is>
       </c>
       <c r="M452" s="4" t="n"/>
@@ -31041,7 +31037,7 @@
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>📝 EAST DEARBORN MEDICAL CLINIC, PC (Medicaid)</t>
+          <t>📝 WARRENFIELD MEDICAL CENTER (Medicaid)</t>
         </is>
       </c>
       <c r="E453" s="4" t="inlineStr">
@@ -31056,7 +31052,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>e73a93c2-41c4-488a-8474-89698cf619bb</t>
+          <t>26dc2847-2f28-4c34-9f35-f5478493d95d</t>
         </is>
       </c>
       <c r="H453" s="3" t="inlineStr">
@@ -31079,7 +31075,7 @@
       </c>
       <c r="L453" s="4" t="inlineStr">
         <is>
-          <t>14650 W WARREN AVE STE 150, DEARBORN, Michigan, 48126</t>
+          <t>14716 W WARREN AVE, DEARBORN, Michigan, 48126</t>
         </is>
       </c>
       <c r="M453" s="4" t="n"/>
@@ -31941,27 +31937,27 @@
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT FAMILY MEDICINE GARDEN CITY</t>
+          <t>📝 MICHIGAN INTERVENTIONAL PAIN CENTER (this is an ASC)</t>
         </is>
       </c>
       <c r="E468" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Aug 21</t>
+          <t>Prospect · last check-in Jan 26</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>796ef668-29ca-4cac-84b8-fd8125eb6bde</t>
+          <t>d1235093-a65c-465a-ace2-cffd3d4ad232</t>
         </is>
       </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I468" s="3" t="inlineStr">
@@ -31974,12 +31970,12 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>29150 FORD RD, GARDEN CITY, MI, 48135</t>
+          <t>24430 Ford Road, Dearborn Heights, Michigan, 48127</t>
         </is>
       </c>
       <c r="M468" s="4" t="n"/>
@@ -32061,12 +32057,12 @@
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>📝 Wayne Primary Care and Walk In</t>
+          <t>📝 BEAUMONT FAMILY MEDICINE GARDEN CITY</t>
         </is>
       </c>
       <c r="E470" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 23</t>
+          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
@@ -32076,12 +32072,12 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>607852d7-cb70-46f8-ac4a-ed6f36b0acf9</t>
+          <t>796ef668-29ca-4cac-84b8-fd8125eb6bde</t>
         </is>
       </c>
       <c r="H470" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I470" s="3" t="inlineStr">
@@ -32094,12 +32090,12 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>Wayne</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>4020 Venoy Rd suite 400, Wayne, Michigan, 48184</t>
+          <t>29150 FORD RD, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M470" s="4" t="n"/>
@@ -32121,27 +32117,27 @@
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT ATHENS CLINIC TAYLOR</t>
+          <t>📝 Wayne Primary Care and Walk In</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Mar 17</t>
+          <t>Tier 2 ortho · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>07d227b8-b9ff-4616-9f9b-f3e3ac05f4b1</t>
+          <t>607852d7-cb70-46f8-ac4a-ed6f36b0acf9</t>
         </is>
       </c>
       <c r="H471" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I471" s="3" t="inlineStr">
@@ -32154,12 +32150,12 @@
       </c>
       <c r="K471" s="3" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="L471" s="4" t="inlineStr">
         <is>
-          <t>15100 S PLAZA DR, TAYLOR, MI, 48180</t>
+          <t>4020 Venoy Rd suite 400, Wayne, Michigan, 48184</t>
         </is>
       </c>
       <c r="M471" s="4" t="n"/>
@@ -33321,45 +33317,45 @@
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>WESTERN WAYNE PHYSICIANS, PLC</t>
+          <t>📝 BEAUMONT ATHENS CLINIC TAYLOR</t>
         </is>
       </c>
       <c r="E491" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Prospect · last check-in Mar 17</t>
         </is>
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>f8ca6ea0-fb53-4992-8eb2-618cc75d56ff</t>
+          <t>07d227b8-b9ff-4616-9f9b-f3e3ac05f4b1</t>
         </is>
       </c>
       <c r="H491" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I491" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J491" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K491" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L491" s="4" t="inlineStr">
         <is>
-          <t>23870 Michigan Ave, Dearborn, MI nan</t>
+          <t>15100 S PLAZA DR, TAYLOR, MI, 48180</t>
         </is>
       </c>
       <c r="M491" s="4" t="n"/>
@@ -33381,36 +33377,36 @@
       </c>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>📝 BRYANT PRIMARY CARE Updated</t>
+          <t>WESTERN WAYNE PHYSICIANS, PLC</t>
         </is>
       </c>
       <c r="E492" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Apr 2</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>5a3b3a92-6b7c-4a66-8877-b58376fa4af0</t>
+          <t>f8ca6ea0-fb53-4992-8eb2-618cc75d56ff</t>
         </is>
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I492" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J492" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
@@ -33419,7 +33415,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>6 parklane Blvd, Suite 436, DEARBORN, Michigan, 48126</t>
+          <t>23870 Michigan Ave, Dearborn, MI nan</t>
         </is>
       </c>
       <c r="M492" s="4" t="n"/>
@@ -34941,27 +34937,27 @@
       </c>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>📝 PelHam Primary Care</t>
+          <t>📝 BRYANT PRIMARY CARE Updated</t>
         </is>
       </c>
       <c r="E518" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Prospect · last check-in Apr 2</t>
         </is>
       </c>
       <c r="F518" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
+          <t>5a3b3a92-6b7c-4a66-8877-b58376fa4af0</t>
         </is>
       </c>
       <c r="H518" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I518" s="3" t="inlineStr">
@@ -34970,7 +34966,7 @@
         </is>
       </c>
       <c r="J518" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
@@ -34979,7 +34975,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
+          <t>6 parklane Blvd, Suite 436, DEARBORN, Michigan, 48126</t>
         </is>
       </c>
       <c r="M518" s="4" t="n"/>
@@ -35001,22 +34997,22 @@
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT FAMILY MEDICINE CLINIC TAYLOR</t>
+          <t>📝 PelHam Primary Care</t>
         </is>
       </c>
       <c r="E519" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Apr 8</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F519" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>ca75c2bf-f7ff-43df-9399-5f78f3147237</t>
+          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
         </is>
       </c>
       <c r="H519" s="3" t="inlineStr">
@@ -35030,16 +35026,16 @@
         </is>
       </c>
       <c r="J519" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K519" s="3" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L519" s="4" t="inlineStr">
         <is>
-          <t>9340 TELEGRAPH RD, TAYLOR, MI, 48180</t>
+          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
         </is>
       </c>
       <c r="M519" s="4" t="n"/>
@@ -35361,12 +35357,12 @@
       </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>📝 WARRENFIELD MEDICAL CENTER (Medicaid)</t>
+          <t>📝 Get Well Urgent Care Southfield</t>
         </is>
       </c>
       <c r="E525" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 1</t>
+          <t>Prospect · last check-in Jun 30</t>
         </is>
       </c>
       <c r="F525" s="3" t="inlineStr">
@@ -35376,12 +35372,12 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>26dc2847-2f28-4c34-9f35-f5478493d95d</t>
+          <t>81a09b96-6834-4950-963a-abff6d4aac6b</t>
         </is>
       </c>
       <c r="H525" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I525" s="3" t="inlineStr">
@@ -35394,12 +35390,12 @@
       </c>
       <c r="K525" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L525" s="4" t="inlineStr">
         <is>
-          <t>14716 W WARREN AVE, DEARBORN, Michigan, 48126</t>
+          <t>23832 Southfield Road, Southfield, Michigan, 48075</t>
         </is>
       </c>
       <c r="M525" s="4" t="n"/>
@@ -35421,27 +35417,27 @@
       </c>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>📝 DEARBORN HEALTHCARE, PC</t>
+          <t>📝 Dedicated Senior Medical Center - Warren</t>
         </is>
       </c>
       <c r="E526" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in May 20</t>
+          <t>Tier 2 ortho · last check-in Oct 8</t>
         </is>
       </c>
       <c r="F526" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2ced9a88-b51d-4a54-a212-063491259282</t>
+          <t>95ae3078-f17c-44de-af58-d9fc8e58f4de</t>
         </is>
       </c>
       <c r="H526" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I526" s="3" t="inlineStr">
@@ -35454,12 +35450,12 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>10066 Dix, Dearborn, Michigan, 48120</t>
+          <t>1921 8 Mile Road, Warren, Michigan, 48091</t>
         </is>
       </c>
       <c r="M526" s="4" t="n"/>
@@ -35481,22 +35477,22 @@
       </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>📝 Evolve Medical - Dearborn</t>
+          <t>📝 Eastpointe Family Physicians</t>
         </is>
       </c>
       <c r="E527" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 17</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>4b035e24-272d-49e7-9bce-cd8929fbcb0a</t>
+          <t>1578685921</t>
         </is>
       </c>
       <c r="H527" s="3" t="inlineStr">
@@ -35510,16 +35506,16 @@
         </is>
       </c>
       <c r="J527" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K527" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Eastpointe</t>
         </is>
       </c>
       <c r="L527" s="4" t="inlineStr">
         <is>
-          <t>9925 Dix Ave, Dearborn, Michigan, 48120</t>
+          <t>24901 Kelly Rd, Eastpointe, MI, 48021</t>
         </is>
       </c>
       <c r="M527" s="4" t="n"/>
@@ -35541,12 +35537,12 @@
       </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>📝 Wayne state Internal Medicine</t>
+          <t>📝 QuickDoc Urgent Care</t>
         </is>
       </c>
       <c r="E528" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F528" s="3" t="inlineStr">
@@ -35556,12 +35552,12 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>39af8a2b-3c99-4502-805c-10e5627efc9d</t>
+          <t>20e3535a-e9f3-4760-9cd8-6e86789495da</t>
         </is>
       </c>
       <c r="H528" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I528" s="3" t="inlineStr">
@@ -35570,16 +35566,16 @@
         </is>
       </c>
       <c r="J528" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Eastpointe</t>
         </is>
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>4201 St Antoine, Detroit, Michigan, 48201</t>
+          <t>19070 East 10 Mile Road, Eastpointe, Michigan, 48021</t>
         </is>
       </c>
       <c r="M528" s="4" t="n"/>
@@ -35601,22 +35597,22 @@
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>📝 Park Medical Center (Medicaid)</t>
+          <t>📝 Office of Douglas Hames MD</t>
         </is>
       </c>
       <c r="E529" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>c4cc522a-15ee-4dcb-8312-cc7b7efdf995</t>
+          <t>1457400954</t>
         </is>
       </c>
       <c r="H529" s="3" t="inlineStr">
@@ -35630,16 +35626,16 @@
         </is>
       </c>
       <c r="J529" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K529" s="3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Eastpointe</t>
         </is>
       </c>
       <c r="L529" s="4" t="inlineStr">
         <is>
-          <t>12871 East Jefferson Avenue, Detroit, Michigan, 48215</t>
+          <t>22850 Kelly Rd, ste 1, Eastpointe, MI, 48021</t>
         </is>
       </c>
       <c r="M529" s="4" t="n"/>
@@ -35721,22 +35717,22 @@
       </c>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>📝 Office of Douglas Hames MD</t>
+          <t>📝 Park Medical Center (Medicaid)</t>
         </is>
       </c>
       <c r="E531" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>1457400954</t>
+          <t>c4cc522a-15ee-4dcb-8312-cc7b7efdf995</t>
         </is>
       </c>
       <c r="H531" s="3" t="inlineStr">
@@ -35750,16 +35746,16 @@
         </is>
       </c>
       <c r="J531" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K531" s="3" t="inlineStr">
         <is>
-          <t>Eastpointe</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L531" s="4" t="inlineStr">
         <is>
-          <t>22850 Kelly Rd, ste 1, Eastpointe, MI, 48021</t>
+          <t>12871 East Jefferson Avenue, Detroit, Michigan, 48215</t>
         </is>
       </c>
       <c r="M531" s="4" t="n"/>
@@ -35781,12 +35777,12 @@
       </c>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>📝 QuickDoc Urgent Care</t>
+          <t>📝 Wayne state Internal Medicine</t>
         </is>
       </c>
       <c r="E532" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F532" s="3" t="inlineStr">
@@ -35796,12 +35792,12 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>20e3535a-e9f3-4760-9cd8-6e86789495da</t>
+          <t>39af8a2b-3c99-4502-805c-10e5627efc9d</t>
         </is>
       </c>
       <c r="H532" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I532" s="3" t="inlineStr">
@@ -35810,16 +35806,16 @@
         </is>
       </c>
       <c r="J532" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>Eastpointe</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>19070 East 10 Mile Road, Eastpointe, Michigan, 48021</t>
+          <t>4201 St Antoine, Detroit, Michigan, 48201</t>
         </is>
       </c>
       <c r="M532" s="4" t="n"/>
@@ -35841,22 +35837,22 @@
       </c>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>📝 Eastpointe Family Physicians</t>
+          <t>📝 Evolve Medical - Dearborn</t>
         </is>
       </c>
       <c r="E533" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Prospect · last check-in Jun 17</t>
         </is>
       </c>
       <c r="F533" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>1578685921</t>
+          <t>4b035e24-272d-49e7-9bce-cd8929fbcb0a</t>
         </is>
       </c>
       <c r="H533" s="3" t="inlineStr">
@@ -35870,16 +35866,16 @@
         </is>
       </c>
       <c r="J533" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K533" s="3" t="inlineStr">
         <is>
-          <t>Eastpointe</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L533" s="4" t="inlineStr">
         <is>
-          <t>24901 Kelly Rd, Eastpointe, MI, 48021</t>
+          <t>9925 Dix Ave, Dearborn, Michigan, 48120</t>
         </is>
       </c>
       <c r="M533" s="4" t="n"/>
@@ -35901,27 +35897,27 @@
       </c>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>📝 Dedicated Senior Medical Center - Warren</t>
+          <t>📝 DEARBORN HEALTHCARE, PC</t>
         </is>
       </c>
       <c r="E534" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Oct 8</t>
+          <t>Prospect · last check-in May 20</t>
         </is>
       </c>
       <c r="F534" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>95ae3078-f17c-44de-af58-d9fc8e58f4de</t>
+          <t>2ced9a88-b51d-4a54-a212-063491259282</t>
         </is>
       </c>
       <c r="H534" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I534" s="3" t="inlineStr">
@@ -35934,12 +35930,12 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>1921 8 Mile Road, Warren, Michigan, 48091</t>
+          <t>10066 Dix, Dearborn, Michigan, 48120</t>
         </is>
       </c>
       <c r="M534" s="4" t="n"/>
@@ -36081,12 +36077,12 @@
       </c>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>📝 ARASH KIARASH, MD, MEDICAL GROUP</t>
+          <t>📝 PARK PLACE FAMILY PRACTICE AND INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="E537" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 29</t>
+          <t>Prospect · last check-in Apr 8</t>
         </is>
       </c>
       <c r="F537" s="3" t="inlineStr">
@@ -36096,12 +36092,12 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>00e2d343-2a6c-4378-900b-c886a064f8a9</t>
+          <t>f8f13fd9-1135-4385-b6ba-7542d202b63a</t>
         </is>
       </c>
       <c r="H537" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I537" s="3" t="inlineStr">
@@ -36119,7 +36115,7 @@
       </c>
       <c r="L537" s="4" t="inlineStr">
         <is>
-          <t>25500 GODDARD RD, TAYLOR, MI, 48180</t>
+          <t>12701 Telegraph Rd, ste 103, TAYLOR, Michigan, 48180</t>
         </is>
       </c>
       <c r="M537" s="4" t="n"/>
@@ -36141,12 +36137,12 @@
       </c>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>📝 PARK PLACE FAMILY PRACTICE AND INTERNAL MEDICINE</t>
+          <t>📝 AMINI HEALTHCARE, PLLC</t>
         </is>
       </c>
       <c r="E538" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Apr 8</t>
+          <t>Prospect · last check-in May 29</t>
         </is>
       </c>
       <c r="F538" s="3" t="inlineStr">
@@ -36156,12 +36152,12 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>f8f13fd9-1135-4385-b6ba-7542d202b63a</t>
+          <t>51be485c-bce1-4997-8e82-1463313f4617</t>
         </is>
       </c>
       <c r="H538" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I538" s="3" t="inlineStr">
@@ -36174,12 +36170,12 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Brownstown Township</t>
         </is>
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>12701 Telegraph Rd, ste 103, TAYLOR, Michigan, 48180</t>
+          <t>19727 Allen Rd, Ste 11, Brownstown Twp, Michigan, 48183</t>
         </is>
       </c>
       <c r="M538" s="4" t="n"/>
@@ -36201,27 +36197,27 @@
       </c>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>📝 AMINI HEALTHCARE, PLLC</t>
+          <t>📝 City Medical - Southgate</t>
         </is>
       </c>
       <c r="E539" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in May 29</t>
+          <t>Tier 2 ortho · last check-in Sep 21</t>
         </is>
       </c>
       <c r="F539" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>51be485c-bce1-4997-8e82-1463313f4617</t>
+          <t>1326021262</t>
         </is>
       </c>
       <c r="H539" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I539" s="3" t="inlineStr">
@@ -36234,12 +36230,12 @@
       </c>
       <c r="K539" s="3" t="inlineStr">
         <is>
-          <t>Brownstown Township</t>
+          <t>Southgate</t>
         </is>
       </c>
       <c r="L539" s="4" t="inlineStr">
         <is>
-          <t>19727 Allen Rd, Ste 11, Brownstown Twp, Michigan, 48183</t>
+          <t>13636 Dix Toledo, Southgate, MI, 481952432</t>
         </is>
       </c>
       <c r="M539" s="4" t="n"/>
@@ -36261,7 +36257,7 @@
       </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>📝 City Medical - Southgate</t>
+          <t>📝 PEDIATRIC AND ADOLESCENT CENTER</t>
         </is>
       </c>
       <c r="E540" s="4" t="inlineStr">
@@ -36276,12 +36272,12 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>1326021262</t>
+          <t>31fe13d8-1060-4c98-bf75-61f09e803121</t>
         </is>
       </c>
       <c r="H540" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I540" s="3" t="inlineStr">
@@ -36299,7 +36295,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>13636 Dix Toledo, Southgate, MI, 481952432</t>
+          <t>15555 Northline Road, Southgate, Michigan, 48195</t>
         </is>
       </c>
       <c r="M540" s="4" t="n"/>
@@ -36321,27 +36317,27 @@
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>📝 PEDIATRIC AND ADOLESCENT CENTER</t>
+          <t>📝 BEAUMONT FAMILY MEDICINE CLINIC TAYLOR</t>
         </is>
       </c>
       <c r="E541" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 21</t>
+          <t>Prospect · last check-in Apr 8</t>
         </is>
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>31fe13d8-1060-4c98-bf75-61f09e803121</t>
+          <t>ca75c2bf-f7ff-43df-9399-5f78f3147237</t>
         </is>
       </c>
       <c r="H541" s="3" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I541" s="3" t="inlineStr">
@@ -36354,12 +36350,12 @@
       </c>
       <c r="K541" s="3" t="inlineStr">
         <is>
-          <t>Southgate</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L541" s="4" t="inlineStr">
         <is>
-          <t>15555 Northline Road, Southgate, Michigan, 48195</t>
+          <t>9340 TELEGRAPH RD, TAYLOR, MI, 48180</t>
         </is>
       </c>
       <c r="M541" s="4" t="n"/>
@@ -38001,22 +37997,22 @@
       </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>📝 BADHWAR ASSOCIATES, MD, PC</t>
+          <t>📝 ARASH KIARASH, MD, MEDICAL GROUP</t>
         </is>
       </c>
       <c r="E569" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in May 29</t>
+          <t>Prospect · last check-in Jun 29</t>
         </is>
       </c>
       <c r="F569" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>930e15d8-29b2-49a1-be3d-7eae0da7dc41</t>
+          <t>00e2d343-2a6c-4378-900b-c886a064f8a9</t>
         </is>
       </c>
       <c r="H569" s="3" t="inlineStr">
@@ -38034,12 +38030,12 @@
       </c>
       <c r="K569" s="3" t="inlineStr">
         <is>
-          <t>Brownstown</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="L569" s="4" t="inlineStr">
         <is>
-          <t>19135 ALLEN RD STE 106, BROWNSTOWN, MI, 48183</t>
+          <t>25500 GODDARD RD, TAYLOR, MI, 48180</t>
         </is>
       </c>
       <c r="M569" s="4" t="n"/>
@@ -38061,12 +38057,12 @@
       </c>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>📝 MD VIP - Trenton</t>
+          <t>📝 BADHWAR ASSOCIATES, MD, PC</t>
         </is>
       </c>
       <c r="E570" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 21</t>
+          <t>Tier 2 ortho · last check-in May 29</t>
         </is>
       </c>
       <c r="F570" s="3" t="inlineStr">
@@ -38076,7 +38072,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>0e7f5d40-b8a0-4524-96a4-2229c7d1e5e7</t>
+          <t>930e15d8-29b2-49a1-be3d-7eae0da7dc41</t>
         </is>
       </c>
       <c r="H570" s="3" t="inlineStr">
@@ -38094,12 +38090,12 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>Trenton</t>
+          <t>Brownstown</t>
         </is>
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>1570 Kingsway Ct suite 1, Trenton, Michigan, 48183</t>
+          <t>19135 ALLEN RD STE 106, BROWNSTOWN, MI, 48183</t>
         </is>
       </c>
       <c r="M570" s="4" t="n"/>
@@ -38121,32 +38117,32 @@
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>MICHAEL DUCATO, MD, PC</t>
+          <t>📝 MD VIP - Trenton</t>
         </is>
       </c>
       <c r="E571" s="4" t="inlineStr">
         <is>
-          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Mar 17</t>
+          <t>Tier 2 ortho · last check-in Sep 21</t>
         </is>
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>1226fb9f-b48d-4314-8a3b-0d8800bc60e1</t>
+          <t>0e7f5d40-b8a0-4524-96a4-2229c7d1e5e7</t>
         </is>
       </c>
       <c r="H571" s="3" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I571" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J571" s="3" t="n">
@@ -38159,7 +38155,7 @@
       </c>
       <c r="L571" s="4" t="inlineStr">
         <is>
-          <t>2901 West Rd, Trenton, MI 48183</t>
+          <t>1570 Kingsway Ct suite 1, Trenton, Michigan, 48183</t>
         </is>
       </c>
       <c r="M571" s="4" t="n"/>
@@ -38168,58 +38164,58 @@
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>J-A01</t>
+          <t>J-A10</t>
         </is>
       </c>
       <c r="C572" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>📝 Grand River Medical Associates</t>
+          <t>MICHAEL DUCATO, MD, PC</t>
         </is>
       </c>
       <c r="E572" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 2</t>
+          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Mar 17</t>
         </is>
       </c>
       <c r="F572" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>218209bd-0e83-4585-b5e7-1455814e77b1</t>
+          <t>1226fb9f-b48d-4314-8a3b-0d8800bc60e1</t>
         </is>
       </c>
       <c r="H572" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I572" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J572" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>New Hudson</t>
+          <t>Trenton</t>
         </is>
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>55840 Grand River Ave ste 300, New Hudson, Michigan, 48165</t>
+          <t>2901 West Rd, Trenton, MI 48183</t>
         </is>
       </c>
       <c r="M572" s="4" t="n"/>
@@ -38237,49 +38233,49 @@
         </is>
       </c>
       <c r="C573" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D573" s="4" t="inlineStr">
+        <is>
+          <t>📝 Grand River Medical Associates</t>
+        </is>
+      </c>
+      <c r="E573" s="4" t="inlineStr">
+        <is>
+          <t>Tier 1 producer · last check-in Oct 2</t>
+        </is>
+      </c>
+      <c r="F573" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G573" s="3" t="inlineStr">
+        <is>
+          <t>218209bd-0e83-4585-b5e7-1455814e77b1</t>
+        </is>
+      </c>
+      <c r="H573" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="I573" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J573" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D573" s="4" t="inlineStr">
-        <is>
-          <t>📝 Karma Internists</t>
-        </is>
-      </c>
-      <c r="E573" s="4" t="inlineStr">
-        <is>
-          <t>Tier 1 producer · last check-in Oct 2</t>
-        </is>
-      </c>
-      <c r="F573" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="G573" s="3" t="inlineStr">
-        <is>
-          <t>9e6bf540-edd8-4135-9b33-cef5e4fbcc2c</t>
-        </is>
-      </c>
-      <c r="H573" s="3" t="inlineStr">
-        <is>
-          <t>PCP</t>
-        </is>
-      </c>
-      <c r="I573" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J573" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="K573" s="3" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>New Hudson</t>
         </is>
       </c>
       <c r="L573" s="4" t="inlineStr">
         <is>
-          <t>26850 PROVIDENCE PKWY STE 420, NOVI, Michigan, 48374</t>
+          <t>55840 Grand River Ave ste 300, New Hudson, Michigan, 48165</t>
         </is>
       </c>
       <c r="M573" s="4" t="n"/>
@@ -38297,16 +38293,16 @@
         </is>
       </c>
       <c r="C574" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>Village Medical - Walled Lake</t>
+          <t>📝 Karma Internists</t>
         </is>
       </c>
       <c r="E574" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Oct 2</t>
         </is>
       </c>
       <c r="F574" s="3" t="inlineStr">
@@ -38316,30 +38312,30 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>6c29d59b-0b61-4f52-b7a7-f29818051f07</t>
+          <t>9e6bf540-edd8-4135-9b33-cef5e4fbcc2c</t>
         </is>
       </c>
       <c r="H574" s="3" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I574" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J574" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>Walled Lake</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>620 N Pontiac Trail, Walled Lake, MI 48390</t>
+          <t>26850 PROVIDENCE PKWY STE 420, NOVI, Michigan, 48374</t>
         </is>
       </c>
       <c r="M574" s="4" t="n"/>
@@ -38357,16 +38353,16 @@
         </is>
       </c>
       <c r="C575" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>📝 DMC SPORTS MEDICINE NOVI</t>
+          <t>Village Medical - Walled Lake</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 2</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F575" s="3" t="inlineStr">
@@ -38376,30 +38372,30 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>6e52135e-6cca-4482-9973-58d180f1dce7</t>
+          <t>6c29d59b-0b61-4f52-b7a7-f29818051f07</t>
         </is>
       </c>
       <c r="H575" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I575" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J575" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K575" s="3" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Walled Lake</t>
         </is>
       </c>
       <c r="L575" s="4" t="inlineStr">
         <is>
-          <t>44000 W 12 MILE RD STE 100, NOVI, MI, 48377</t>
+          <t>620 N Pontiac Trail, Walled Lake, MI 48390</t>
         </is>
       </c>
       <c r="M575" s="4" t="n"/>
@@ -38417,16 +38413,16 @@
         </is>
       </c>
       <c r="C576" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>📝 NORLIVO INTERNAL MEDICINE</t>
+          <t>📝 DMC SPORTS MEDICINE NOVI</t>
         </is>
       </c>
       <c r="E576" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Oct 2</t>
         </is>
       </c>
       <c r="F576" s="3" t="inlineStr">
@@ -38436,7 +38432,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>74262c96-dd4b-4b92-acd7-c43ebba4c04f</t>
+          <t>6e52135e-6cca-4482-9973-58d180f1dce7</t>
         </is>
       </c>
       <c r="H576" s="3" t="inlineStr">
@@ -38450,16 +38446,16 @@
         </is>
       </c>
       <c r="J576" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>20311 Farmington Road, Livonia, Michigan, 48152</t>
+          <t>44000 W 12 MILE RD STE 100, NOVI, MI, 48377</t>
         </is>
       </c>
       <c r="M576" s="4" t="n"/>
@@ -38477,16 +38473,16 @@
         </is>
       </c>
       <c r="C577" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>📝 Freedom Medical Clinic (Trinity)</t>
+          <t>📝 NORLIVO INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F577" s="3" t="inlineStr">
@@ -38496,12 +38492,12 @@
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>e0d8c74a-31fe-4da6-9aa4-6a2357088b6a</t>
+          <t>74262c96-dd4b-4b92-acd7-c43ebba4c04f</t>
         </is>
       </c>
       <c r="H577" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I577" s="3" t="inlineStr">
@@ -38510,7 +38506,7 @@
         </is>
       </c>
       <c r="J577" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K577" s="3" t="inlineStr">
         <is>
@@ -38519,7 +38515,7 @@
       </c>
       <c r="L577" s="4" t="inlineStr">
         <is>
-          <t>20206 Farmington Rd, Livonia, MI, 48152</t>
+          <t>20311 Farmington Road, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M577" s="4" t="n"/>
@@ -38537,16 +38533,16 @@
         </is>
       </c>
       <c r="C578" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>Trinity IHA Orthopedics - Schoolcraft</t>
+          <t>📝 Freedom Medical Clinic (Trinity)</t>
         </is>
       </c>
       <c r="E578" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F578" s="3" t="inlineStr">
@@ -38556,12 +38552,12 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>e5c5b135-ecad-42bb-bbbc-011dd2c4a225</t>
+          <t>e0d8c74a-31fe-4da6-9aa4-6a2357088b6a</t>
         </is>
       </c>
       <c r="H578" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I578" s="3" t="inlineStr">
@@ -38579,7 +38575,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>19000 St Joe's Pkwy, Livonia, Michigan, 48152</t>
+          <t>20206 Farmington Rd, Livonia, MI, 48152</t>
         </is>
       </c>
       <c r="M578" s="4" t="n"/>
@@ -38597,16 +38593,16 @@
         </is>
       </c>
       <c r="C579" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>📝 Lakes Urgent Care - Livonia</t>
+          <t>Trinity IHA Orthopedics - Schoolcraft</t>
         </is>
       </c>
       <c r="E579" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F579" s="3" t="inlineStr">
@@ -38616,12 +38612,12 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>73107e68-fc7f-46d0-bef4-ee26e9dc0099</t>
+          <t>e5c5b135-ecad-42bb-bbbc-011dd2c4a225</t>
         </is>
       </c>
       <c r="H579" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I579" s="3" t="inlineStr">
@@ -38639,7 +38635,7 @@
       </c>
       <c r="L579" s="4" t="inlineStr">
         <is>
-          <t>36650 Five Mile Rd suite 106, Livonia, Michigan, 48154</t>
+          <t>19000 St Joe's Pkwy, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M579" s="4" t="n"/>
@@ -38657,16 +38653,16 @@
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>📝 Comprehensive Healthcare Associates and Prevention Medicine</t>
+          <t>📝 Lakes Urgent Care - Livonia</t>
         </is>
       </c>
       <c r="E580" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F580" s="3" t="inlineStr">
@@ -38676,12 +38672,12 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>c7781046-a235-49fa-ac8e-4b8d6354c618</t>
+          <t>73107e68-fc7f-46d0-bef4-ee26e9dc0099</t>
         </is>
       </c>
       <c r="H580" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I580" s="3" t="inlineStr">
@@ -38690,7 +38686,7 @@
         </is>
       </c>
       <c r="J580" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
@@ -38699,7 +38695,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>15140 Levan Rd, Livonia, Michigan, 48154</t>
+          <t>36650 Five Mile Rd suite 106, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M580" s="4" t="n"/>
@@ -38717,31 +38713,31 @@
         </is>
       </c>
       <c r="C581" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>All-Pro Physical Therapy</t>
+          <t>📝 Comprehensive Healthcare Associates and Prevention Medicine</t>
         </is>
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 23</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>9531e09a-b183-4d68-994a-80342d7b0c2e</t>
+          <t>c7781046-a235-49fa-ac8e-4b8d6354c618</t>
         </is>
       </c>
       <c r="H581" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I581" s="3" t="inlineStr">
@@ -38750,16 +38746,16 @@
         </is>
       </c>
       <c r="J581" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K581" s="3" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L581" s="4" t="inlineStr">
         <is>
-          <t>43050 Ford Road, Canton, Michigan, 48187</t>
+          <t>15140 Levan Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M581" s="4" t="n"/>
@@ -38773,30 +38769,30 @@
       </c>
       <c r="B582" s="3" t="inlineStr">
         <is>
-          <t>J-A06</t>
+          <t>J-A01</t>
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>📝 Michigan Urgent Care - Livonia</t>
+          <t>All-Pro Physical Therapy</t>
         </is>
       </c>
       <c r="E582" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Aug 31</t>
+          <t>Prospect · last check-in Jul 23</t>
         </is>
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>1d453948-16d6-4da0-a7d9-80b603bedb9b</t>
+          <t>9531e09a-b183-4d68-994a-80342d7b0c2e</t>
         </is>
       </c>
       <c r="H582" s="3" t="inlineStr">
@@ -38814,12 +38810,12 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>37595 W Seven Mile Rd, Livonia, Michigan, 48152</t>
+          <t>43050 Ford Road, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M582" s="4" t="n"/>
@@ -38837,16 +38833,16 @@
         </is>
       </c>
       <c r="C583" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>📝 Trinity IHA Academic Family Medicine - Livonia</t>
+          <t>📝 Michigan Urgent Care - Livonia</t>
         </is>
       </c>
       <c r="E583" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 31</t>
+          <t>Tier 2 ortho · last check-in Aug 31</t>
         </is>
       </c>
       <c r="F583" s="3" t="inlineStr">
@@ -38856,12 +38852,12 @@
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>5c7c8073-5fc6-42f5-bc75-0b9f8a07e484</t>
+          <t>1d453948-16d6-4da0-a7d9-80b603bedb9b</t>
         </is>
       </c>
       <c r="H583" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I583" s="3" t="inlineStr">
@@ -38879,7 +38875,7 @@
       </c>
       <c r="L583" s="4" t="inlineStr">
         <is>
-          <t>37595 7 mile rd, ste 210, LIVONIA, Michigan, 48152</t>
+          <t>37595 W Seven Mile Rd, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M583" s="4" t="n"/>
@@ -38897,16 +38893,16 @@
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>📝 UNIVERSITY OF MICHIGAN LIVONIA HEALTH CENTER</t>
+          <t>📝 Trinity IHA Academic Family Medicine - Livonia</t>
         </is>
       </c>
       <c r="E584" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 14</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 31</t>
         </is>
       </c>
       <c r="F584" s="3" t="inlineStr">
@@ -38916,12 +38912,12 @@
       </c>
       <c r="G584" s="3" t="inlineStr">
         <is>
-          <t>fcafa62b-aa2e-4816-b546-f6718ff3ece8</t>
+          <t>5c7c8073-5fc6-42f5-bc75-0b9f8a07e484</t>
         </is>
       </c>
       <c r="H584" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I584" s="3" t="inlineStr">
@@ -38939,7 +38935,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>20321 FARMINGTON RD, LIVONIA, MI, 48152</t>
+          <t>37595 7 mile rd, ste 210, LIVONIA, Michigan, 48152</t>
         </is>
       </c>
       <c r="M584" s="4" t="n"/>
@@ -38957,16 +38953,16 @@
         </is>
       </c>
       <c r="C585" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>📝 CENTER FOR INTERNAL MEDICINE CONTINUITY CLINIC</t>
+          <t>📝 UNIVERSITY OF MICHIGAN LIVONIA HEALTH CENTER</t>
         </is>
       </c>
       <c r="E585" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Aug 14</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 14</t>
         </is>
       </c>
       <c r="F585" s="3" t="inlineStr">
@@ -38976,7 +38972,7 @@
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>ce969d89-5e72-4361-9024-039ad31f5bc3</t>
+          <t>fcafa62b-aa2e-4816-b546-f6718ff3ece8</t>
         </is>
       </c>
       <c r="H585" s="3" t="inlineStr">
@@ -38999,7 +38995,7 @@
       </c>
       <c r="L585" s="4" t="inlineStr">
         <is>
-          <t>28479 7 MILE RD, LIVONIA, MI, 48152</t>
+          <t>20321 FARMINGTON RD, LIVONIA, MI, 48152</t>
         </is>
       </c>
       <c r="M585" s="4" t="n"/>
@@ -39017,16 +39013,16 @@
         </is>
       </c>
       <c r="C586" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT FAMILY MEDICINE GARDEN CITY</t>
+          <t>📝 CENTER FOR INTERNAL MEDICINE CONTINUITY CLINIC</t>
         </is>
       </c>
       <c r="E586" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Aug 21</t>
+          <t>Tier 2 ortho · last check-in Aug 14</t>
         </is>
       </c>
       <c r="F586" s="3" t="inlineStr">
@@ -39036,7 +39032,7 @@
       </c>
       <c r="G586" s="3" t="inlineStr">
         <is>
-          <t>796ef668-29ca-4cac-84b8-fd8125eb6bde</t>
+          <t>ce969d89-5e72-4361-9024-039ad31f5bc3</t>
         </is>
       </c>
       <c r="H586" s="3" t="inlineStr">
@@ -39054,12 +39050,12 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>29150 FORD RD, GARDEN CITY, MI, 48135</t>
+          <t>28479 7 MILE RD, LIVONIA, MI, 48152</t>
         </is>
       </c>
       <c r="M586" s="4" t="n"/>
@@ -39077,16 +39073,16 @@
         </is>
       </c>
       <c r="C587" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>Michigan primary care center/urgent care</t>
+          <t>📝 BEAUMONT FAMILY MEDICINE GARDEN CITY</t>
         </is>
       </c>
       <c r="E587" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 24</t>
+          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Aug 21</t>
         </is>
       </c>
       <c r="F587" s="3" t="inlineStr">
@@ -39096,17 +39092,17 @@
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>3b12c579-0694-4d99-9a66-96f56d80d5e7</t>
+          <t>796ef668-29ca-4cac-84b8-fd8125eb6bde</t>
         </is>
       </c>
       <c r="H587" s="3" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I587" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J587" s="3" t="n">
@@ -39114,12 +39110,12 @@
       </c>
       <c r="K587" s="3" t="inlineStr">
         <is>
-          <t>Dearborn Heights</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L587" s="4" t="inlineStr">
         <is>
-          <t>27250 Cherry Hill Road, Dearborn Heights, MI 48127</t>
+          <t>29150 FORD RD, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M587" s="4" t="n"/>
@@ -39137,16 +39133,16 @@
         </is>
       </c>
       <c r="C588" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>The family Doc</t>
+          <t>Michigan primary care center/urgent care</t>
         </is>
       </c>
       <c r="E588" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 23</t>
+          <t>Tier 2 ortho · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F588" s="3" t="inlineStr">
@@ -39156,17 +39152,17 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>3b5d6ffd-3a5a-4ccd-b656-e2340f7c8ea5</t>
+          <t>3b12c579-0694-4d99-9a66-96f56d80d5e7</t>
         </is>
       </c>
       <c r="H588" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I588" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J588" s="3" t="n">
@@ -39179,7 +39175,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>25350 West Warren Street, Dearborn Heights, Michigan, 48127</t>
+          <t>27250 Cherry Hill Road, Dearborn Heights, MI 48127</t>
         </is>
       </c>
       <c r="M588" s="4" t="n"/>
@@ -39197,26 +39193,26 @@
         </is>
       </c>
       <c r="C589" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>📝 TENNY INTERNAL MEDICINE, PLLC</t>
+          <t>The family Doc</t>
         </is>
       </c>
       <c r="E589" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 2 ortho · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>3effe9bc-8576-4eee-ba7e-9bf99eb7d1fa</t>
+          <t>3b5d6ffd-3a5a-4ccd-b656-e2340f7c8ea5</t>
         </is>
       </c>
       <c r="H589" s="3" t="inlineStr">
@@ -39230,16 +39226,16 @@
         </is>
       </c>
       <c r="J589" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K589" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Dearborn Heights</t>
         </is>
       </c>
       <c r="L589" s="4" t="inlineStr">
         <is>
-          <t>22361 W VILLAGE DR STE 102, DEARBORN, MI, 48124</t>
+          <t>25350 West Warren Street, Dearborn Heights, Michigan, 48127</t>
         </is>
       </c>
       <c r="M589" s="4" t="n"/>
@@ -39257,16 +39253,16 @@
         </is>
       </c>
       <c r="C590" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>📝 PelHam Primary Care</t>
+          <t>📝 TENNY INTERNAL MEDICINE, PLLC</t>
         </is>
       </c>
       <c r="E590" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F590" s="3" t="inlineStr">
@@ -39276,7 +39272,7 @@
       </c>
       <c r="G590" s="3" t="inlineStr">
         <is>
-          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
+          <t>3effe9bc-8576-4eee-ba7e-9bf99eb7d1fa</t>
         </is>
       </c>
       <c r="H590" s="3" t="inlineStr">
@@ -39299,7 +39295,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
+          <t>22361 W VILLAGE DR STE 102, DEARBORN, MI, 48124</t>
         </is>
       </c>
       <c r="M590" s="4" t="n"/>
@@ -39317,26 +39313,26 @@
         </is>
       </c>
       <c r="C591" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>📝 Dearborn Health Clinic</t>
+          <t>📝 PelHam Primary Care</t>
         </is>
       </c>
       <c r="E591" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 14</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G591" s="3" t="inlineStr">
         <is>
-          <t>e1b0659f-dd0b-44de-bb56-320215093e67</t>
+          <t>d4c2e8cb-a4bb-454f-bc5c-8425cff6d293</t>
         </is>
       </c>
       <c r="H591" s="3" t="inlineStr">
@@ -39350,7 +39346,7 @@
         </is>
       </c>
       <c r="J591" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K591" s="3" t="inlineStr">
         <is>
@@ -39359,7 +39355,7 @@
       </c>
       <c r="L591" s="4" t="inlineStr">
         <is>
-          <t>13840 W Warren Ave, Dearborn, Michigan, 48126</t>
+          <t>3815 Pelham Street, Dearborn, Michigan, 48124</t>
         </is>
       </c>
       <c r="M591" s="4" t="n"/>
@@ -39373,30 +39369,30 @@
       </c>
       <c r="B592" s="3" t="inlineStr">
         <is>
-          <t>J-A07</t>
+          <t>J-A06</t>
         </is>
       </c>
       <c r="C592" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>📝 Trinity Health IHA Medical Group, Primary Care - Southeast Livonia</t>
+          <t>📝 Corwell health internal medicine, Dearborn</t>
         </is>
       </c>
       <c r="E592" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 28</t>
+          <t>Prospect · last check-in Jul 14</t>
         </is>
       </c>
       <c r="F592" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G592" s="3" t="inlineStr">
         <is>
-          <t>6b70f9d5-4063-4208-85f4-1d780fabaacc</t>
+          <t>1881654705</t>
         </is>
       </c>
       <c r="H592" s="3" t="inlineStr">
@@ -39410,16 +39406,16 @@
         </is>
       </c>
       <c r="J592" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>29370 Plymouth Road, Livonia, Michigan, 48150</t>
+          <t>4700 Schaefer Rd, Suite 240, Dearborn, MI, 481263698</t>
         </is>
       </c>
       <c r="M592" s="4" t="n"/>
@@ -39437,16 +39433,16 @@
         </is>
       </c>
       <c r="C593" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>📝 Livonia Family Medical Center</t>
+          <t>📝 Trinity Health IHA Medical Group, Primary Care - Southeast Livonia</t>
         </is>
       </c>
       <c r="E593" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
+          <t>Tier 1 producer · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F593" s="3" t="inlineStr">
@@ -39456,7 +39452,7 @@
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>68ceff67-99ac-4ef7-a162-918f93bbdf38</t>
+          <t>6b70f9d5-4063-4208-85f4-1d780fabaacc</t>
         </is>
       </c>
       <c r="H593" s="3" t="inlineStr">
@@ -39479,7 +39475,7 @@
       </c>
       <c r="L593" s="4" t="inlineStr">
         <is>
-          <t>28701 Plymouth Rd, Livonia, Michigan, 48150</t>
+          <t>29370 Plymouth Road, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M593" s="4" t="n"/>
@@ -39497,16 +39493,16 @@
         </is>
       </c>
       <c r="C594" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>📝 Synergy Medical Primary Care</t>
+          <t>📝 Livonia Family Medical Center</t>
         </is>
       </c>
       <c r="E594" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 25</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F594" s="3" t="inlineStr">
@@ -39516,7 +39512,7 @@
       </c>
       <c r="G594" s="3" t="inlineStr">
         <is>
-          <t>5cb01f9c-faec-4c04-b600-f0eba085f6a3</t>
+          <t>68ceff67-99ac-4ef7-a162-918f93bbdf38</t>
         </is>
       </c>
       <c r="H594" s="3" t="inlineStr">
@@ -39530,7 +39526,7 @@
         </is>
       </c>
       <c r="J594" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
@@ -39539,7 +39535,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>9216 Middlebelt Rd, Livonia, Michigan, 48150</t>
+          <t>28701 Plymouth Rd, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M594" s="4" t="n"/>
@@ -39557,49 +39553,49 @@
         </is>
       </c>
       <c r="C595" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D595" s="4" t="inlineStr">
+        <is>
+          <t>📝 Synergy Medical Primary Care</t>
+        </is>
+      </c>
+      <c r="E595" s="4" t="inlineStr">
+        <is>
+          <t>Tier 1 producer · last check-in Sep 25</t>
+        </is>
+      </c>
+      <c r="F595" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G595" s="3" t="inlineStr">
+        <is>
+          <t>5cb01f9c-faec-4c04-b600-f0eba085f6a3</t>
+        </is>
+      </c>
+      <c r="H595" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="I595" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J595" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D595" s="4" t="inlineStr">
-        <is>
-          <t>📝 APOLLO HEALTH SERVICES, PC</t>
-        </is>
-      </c>
-      <c r="E595" s="4" t="inlineStr">
-        <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
-        </is>
-      </c>
-      <c r="F595" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="G595" s="3" t="inlineStr">
-        <is>
-          <t>1689099f-fc6b-4174-9111-5dce70adbd66</t>
-        </is>
-      </c>
-      <c r="H595" s="3" t="inlineStr">
-        <is>
-          <t>PCP</t>
-        </is>
-      </c>
-      <c r="I595" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J595" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="K595" s="3" t="inlineStr">
         <is>
-          <t>Garden City</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L595" s="4" t="inlineStr">
         <is>
-          <t>5823 MIDDLEBELT RD, GARDEN CITY, MI, 48135</t>
+          <t>9216 Middlebelt Rd, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M595" s="4" t="n"/>
@@ -39617,11 +39613,11 @@
         </is>
       </c>
       <c r="C596" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>📝 Plymouth physical therapy services</t>
+          <t>📝 APOLLO HEALTH SERVICES, PC</t>
         </is>
       </c>
       <c r="E596" s="4" t="inlineStr">
@@ -39636,12 +39632,12 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>cd5ff85f-ef03-49bb-bf33-ee98e3b500ec</t>
+          <t>1689099f-fc6b-4174-9111-5dce70adbd66</t>
         </is>
       </c>
       <c r="H596" s="3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I596" s="3" t="inlineStr">
@@ -39659,7 +39655,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>29454 Ford Road, Garden City, Michigan, 48135</t>
+          <t>5823 MIDDLEBELT RD, GARDEN CITY, MI, 48135</t>
         </is>
       </c>
       <c r="M596" s="4" t="n"/>
@@ -39677,11 +39673,11 @@
         </is>
       </c>
       <c r="C597" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>📝 OAK STREET HEALTH CHERRY HILL</t>
+          <t>📝 Plymouth physical therapy services</t>
         </is>
       </c>
       <c r="E597" s="4" t="inlineStr">
@@ -39696,12 +39692,12 @@
       </c>
       <c r="G597" s="3" t="inlineStr">
         <is>
-          <t>0cc06713-910b-4b74-ba14-7cd3d76b3c62</t>
+          <t>cd5ff85f-ef03-49bb-bf33-ee98e3b500ec</t>
         </is>
       </c>
       <c r="H597" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I597" s="3" t="inlineStr">
@@ -39710,16 +39706,16 @@
         </is>
       </c>
       <c r="J597" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K597" s="3" t="inlineStr">
         <is>
-          <t>Inkster</t>
+          <t>Garden City</t>
         </is>
       </c>
       <c r="L597" s="4" t="inlineStr">
         <is>
-          <t>27155 CHERRY HILL RD, INKSTER, MI, 48141</t>
+          <t>29454 Ford Road, Garden City, Michigan, 48135</t>
         </is>
       </c>
       <c r="M597" s="4" t="n"/>
@@ -39737,16 +39733,16 @@
         </is>
       </c>
       <c r="C598" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>WESTERN WAYNE PHYSICIANS, PLC</t>
+          <t>📝 OAK STREET HEALTH CHERRY HILL</t>
         </is>
       </c>
       <c r="E598" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F598" s="3" t="inlineStr">
@@ -39756,30 +39752,30 @@
       </c>
       <c r="G598" s="3" t="inlineStr">
         <is>
-          <t>f8ca6ea0-fb53-4992-8eb2-618cc75d56ff</t>
+          <t>0cc06713-910b-4b74-ba14-7cd3d76b3c62</t>
         </is>
       </c>
       <c r="H598" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I598" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J598" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Inkster</t>
         </is>
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>23870 Michigan Ave, Dearborn, MI nan</t>
+          <t>27155 CHERRY HILL RD, INKSTER, MI, 48141</t>
         </is>
       </c>
       <c r="M598" s="4" t="n"/>
@@ -39797,16 +39793,16 @@
         </is>
       </c>
       <c r="C599" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>📝 Frank Lanzilote DO-Family Practice</t>
+          <t>WESTERN WAYNE PHYSICIANS, PLC</t>
         </is>
       </c>
       <c r="E599" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 17</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F599" s="3" t="inlineStr">
@@ -39816,30 +39812,30 @@
       </c>
       <c r="G599" s="3" t="inlineStr">
         <is>
-          <t>1d143d90-6122-41e7-ae14-c14d4e4317b4</t>
+          <t>f8ca6ea0-fb53-4992-8eb2-618cc75d56ff</t>
         </is>
       </c>
       <c r="H599" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I599" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J599" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K599" s="3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L599" s="4" t="inlineStr">
         <is>
-          <t>16226 Grand River Ave, Detroit, Michigan, 48227</t>
+          <t>23870 Michigan Ave, Dearborn, MI nan</t>
         </is>
       </c>
       <c r="M599" s="4" t="n"/>
@@ -39857,26 +39853,26 @@
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>📝 Dedicated senior Medical Center Detroit North</t>
+          <t>📝 Oakman, Medical Center</t>
         </is>
       </c>
       <c r="E600" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
+          <t>Prospect · last check-in Jul 14</t>
         </is>
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G600" s="3" t="inlineStr">
         <is>
-          <t>85d28577-5be8-4372-8c7e-9a349c62e50d</t>
+          <t>9ae9d844-759e-42b5-a563-2ad00aab5748</t>
         </is>
       </c>
       <c r="H600" s="3" t="inlineStr">
@@ -39890,16 +39886,16 @@
         </is>
       </c>
       <c r="J600" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>20001 West Seven Mile Road, Detroit, Michigan, 48219</t>
+          <t>5280 Oakman Blvd, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M600" s="4" t="n"/>
@@ -39917,31 +39913,31 @@
         </is>
       </c>
       <c r="C601" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>📝 Get Well Urgent Care Southfield</t>
+          <t>📝 Frank Lanzilote DO-Family Practice</t>
         </is>
       </c>
       <c r="E601" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 30</t>
+          <t>Tier 1 producer · last check-in Sep 17</t>
         </is>
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>81a09b96-6834-4950-963a-abff6d4aac6b</t>
+          <t>1d143d90-6122-41e7-ae14-c14d4e4317b4</t>
         </is>
       </c>
       <c r="H601" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I601" s="3" t="inlineStr">
@@ -39950,16 +39946,16 @@
         </is>
       </c>
       <c r="J601" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K601" s="3" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L601" s="4" t="inlineStr">
         <is>
-          <t>23832 Southfield Road, Southfield, Michigan, 48075</t>
+          <t>16226 Grand River Ave, Detroit, Michigan, 48227</t>
         </is>
       </c>
       <c r="M601" s="4" t="n"/>
@@ -39973,20 +39969,20 @@
       </c>
       <c r="B602" s="3" t="inlineStr">
         <is>
-          <t>J-A09</t>
+          <t>J-A07</t>
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>📝 Corewell Health Wayne Hospital Family Medicine -  Canton</t>
+          <t>📝 Dedicated senior Medical Center Detroit North</t>
         </is>
       </c>
       <c r="E602" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 30</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F602" s="3" t="inlineStr">
@@ -39996,7 +39992,7 @@
       </c>
       <c r="G602" s="3" t="inlineStr">
         <is>
-          <t>1022591b-a2f2-47ed-a718-e764042f930d</t>
+          <t>85d28577-5be8-4372-8c7e-9a349c62e50d</t>
         </is>
       </c>
       <c r="H602" s="3" t="inlineStr">
@@ -40014,12 +40010,12 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>7330 N CANTON CENTER RD STE 111, CANTON, MI, 48187</t>
+          <t>20001 West Seven Mile Road, Detroit, Michigan, 48219</t>
         </is>
       </c>
       <c r="M602" s="4" t="n"/>
@@ -40037,31 +40033,31 @@
         </is>
       </c>
       <c r="C603" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>CANTON FOOT &amp; Ankle SPECIALISTS</t>
+          <t>📝 Corewell Health Wayne Hospital Family Medicine -  Canton</t>
         </is>
       </c>
       <c r="E603" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 23</t>
+          <t>Tier 1 producer · last check-in Sep 30</t>
         </is>
       </c>
       <c r="F603" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>13dc6a74-7486-4022-8993-7eaf6b95734e</t>
+          <t>1022591b-a2f2-47ed-a718-e764042f930d</t>
         </is>
       </c>
       <c r="H603" s="3" t="inlineStr">
         <is>
-          <t>Podiatry</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I603" s="3" t="inlineStr">
@@ -40070,7 +40066,7 @@
         </is>
       </c>
       <c r="J603" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K603" s="3" t="inlineStr">
         <is>
@@ -40079,7 +40075,7 @@
       </c>
       <c r="L603" s="4" t="inlineStr">
         <is>
-          <t>43050 Ford Road Ste 150, Canton, Michigan, 48187</t>
+          <t>7330 N CANTON CENTER RD STE 111, CANTON, MI, 48187</t>
         </is>
       </c>
       <c r="M603" s="4" t="n"/>
@@ -40097,31 +40093,31 @@
         </is>
       </c>
       <c r="C604" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>Michigan family wellness</t>
+          <t>CANTON FOOT &amp; Ankle SPECIALISTS</t>
         </is>
       </c>
       <c r="E604" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 1</t>
+          <t>Tier 2 ortho · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F604" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G604" s="3" t="inlineStr">
         <is>
-          <t>99d4fe31-7800-4760-b438-523fa51d9e6b</t>
+          <t>13dc6a74-7486-4022-8993-7eaf6b95734e</t>
         </is>
       </c>
       <c r="H604" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Podiatry</t>
         </is>
       </c>
       <c r="I604" s="3" t="inlineStr">
@@ -40130,7 +40126,7 @@
         </is>
       </c>
       <c r="J604" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
@@ -40139,7 +40135,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2050 North Haggerty Road, CANTON, Michigan, 48187</t>
+          <t>43050 Ford Road Ste 150, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M604" s="4" t="n"/>
@@ -40157,31 +40153,31 @@
         </is>
       </c>
       <c r="C605" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>📝 Wayne Primary Care and Walk In</t>
+          <t>Michigan family wellness</t>
         </is>
       </c>
       <c r="E605" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 23</t>
+          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F605" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G605" s="3" t="inlineStr">
         <is>
-          <t>607852d7-cb70-46f8-ac4a-ed6f36b0acf9</t>
+          <t>99d4fe31-7800-4760-b438-523fa51d9e6b</t>
         </is>
       </c>
       <c r="H605" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I605" s="3" t="inlineStr">
@@ -40190,16 +40186,16 @@
         </is>
       </c>
       <c r="J605" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K605" s="3" t="inlineStr">
         <is>
-          <t>Wayne</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="L605" s="4" t="inlineStr">
         <is>
-          <t>4020 Venoy Rd suite 400, Wayne, Michigan, 48184</t>
+          <t>2050 North Haggerty Road, CANTON, Michigan, 48187</t>
         </is>
       </c>
       <c r="M605" s="4" t="n"/>
@@ -40217,31 +40213,31 @@
         </is>
       </c>
       <c r="C606" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>📝 DEARBORN FAMILY CLINIC, PC</t>
+          <t>📝 Wayne Primary Care and Walk In</t>
         </is>
       </c>
       <c r="E606" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 2 ortho · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F606" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>a7a3d5c1-7a49-46bc-b9ad-08cbe9188e80</t>
+          <t>607852d7-cb70-46f8-ac4a-ed6f36b0acf9</t>
         </is>
       </c>
       <c r="H606" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I606" s="3" t="inlineStr">
@@ -40250,16 +40246,16 @@
         </is>
       </c>
       <c r="J606" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>3133 South Telegraph Road, Dearborn, Michigan, 48124</t>
+          <t>4020 Venoy Rd suite 400, Wayne, Michigan, 48184</t>
         </is>
       </c>
       <c r="M606" s="4" t="n"/>
@@ -40277,31 +40273,31 @@
         </is>
       </c>
       <c r="C607" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>📝 Oakman, Medical Center</t>
+          <t>📝 DEARBORN FAMILY CLINIC, PC</t>
         </is>
       </c>
       <c r="E607" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 14</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G607" s="3" t="inlineStr">
         <is>
-          <t>9ae9d844-759e-42b5-a563-2ad00aab5748</t>
+          <t>a7a3d5c1-7a49-46bc-b9ad-08cbe9188e80</t>
         </is>
       </c>
       <c r="H607" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I607" s="3" t="inlineStr">
@@ -40310,7 +40306,7 @@
         </is>
       </c>
       <c r="J607" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K607" s="3" t="inlineStr">
         <is>
@@ -40319,7 +40315,7 @@
       </c>
       <c r="L607" s="4" t="inlineStr">
         <is>
-          <t>5280 Oakman Blvd, Dearborn, Michigan, 48126</t>
+          <t>3133 South Telegraph Road, Dearborn, Michigan, 48124</t>
         </is>
       </c>
       <c r="M607" s="4" t="n"/>
@@ -40337,26 +40333,26 @@
         </is>
       </c>
       <c r="C608" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>BN Nandish MD</t>
+          <t>📝 Dearborn Health Clinic</t>
         </is>
       </c>
       <c r="E608" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 28</t>
+          <t>Prospect · last check-in Jul 14</t>
         </is>
       </c>
       <c r="F608" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>4dee089f-61d1-4d13-9fca-62b8d8ffc312</t>
+          <t>e1b0659f-dd0b-44de-bb56-320215093e67</t>
         </is>
       </c>
       <c r="H608" s="3" t="inlineStr">
@@ -40374,12 +40370,12 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>14555 Levan Rd suite 308, Livonia, Michigan, 48154</t>
+          <t>13840 W Warren Ave, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M608" s="4" t="n"/>
@@ -40397,11 +40393,11 @@
         </is>
       </c>
       <c r="C609" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>📝 Western Wayne Physicians - Livonia</t>
+          <t>BN Nandish MD</t>
         </is>
       </c>
       <c r="E609" s="4" t="inlineStr">
@@ -40416,7 +40412,7 @@
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>c6f8c7f7-2386-4788-9102-c4f9ebda94b8</t>
+          <t>4dee089f-61d1-4d13-9fca-62b8d8ffc312</t>
         </is>
       </c>
       <c r="H609" s="3" t="inlineStr">
@@ -40439,7 +40435,7 @@
       </c>
       <c r="L609" s="4" t="inlineStr">
         <is>
-          <t>15160 Levan Rd, Livonia, Michigan, 48154</t>
+          <t>14555 Levan Rd suite 308, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M609" s="4" t="n"/>
@@ -40457,26 +40453,26 @@
         </is>
       </c>
       <c r="C610" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>📝 Levan Internists</t>
+          <t>📝 Western Wayne Physicians - Livonia</t>
         </is>
       </c>
       <c r="E610" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
+          <t>Tier 2 ortho · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F610" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G610" s="3" t="inlineStr">
         <is>
-          <t>1972528818</t>
+          <t>c6f8c7f7-2386-4788-9102-c4f9ebda94b8</t>
         </is>
       </c>
       <c r="H610" s="3" t="inlineStr">
@@ -40490,7 +40486,7 @@
         </is>
       </c>
       <c r="J610" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
@@ -40499,7 +40495,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>15130 Levan Rd, Livonia, MI, 48154</t>
+          <t>15160 Levan Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M610" s="4" t="n"/>
@@ -40517,26 +40513,26 @@
         </is>
       </c>
       <c r="C611" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>📝 *NOVAMEDICA, PLLC</t>
+          <t>📝 Levan Internists</t>
         </is>
       </c>
       <c r="E611" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 14</t>
+          <t>Tier 1 producer · tier Tier 2→Tier 1 (Sep 22) · last check-in Sep 28</t>
         </is>
       </c>
       <c r="F611" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>d2a011ae-fad5-4195-a59b-93376dd15321</t>
+          <t>1972528818</t>
         </is>
       </c>
       <c r="H611" s="3" t="inlineStr">
@@ -40550,7 +40546,7 @@
         </is>
       </c>
       <c r="J611" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K611" s="3" t="inlineStr">
         <is>
@@ -40559,7 +40555,7 @@
       </c>
       <c r="L611" s="4" t="inlineStr">
         <is>
-          <t>20331 FARMINGTON RD STE 103, LIVONIA, MI, 48152</t>
+          <t>15130 Levan Rd, Livonia, MI, 48154</t>
         </is>
       </c>
       <c r="M611" s="4" t="n"/>
@@ -40573,20 +40569,20 @@
       </c>
       <c r="B612" s="3" t="inlineStr">
         <is>
-          <t>J-A11</t>
+          <t>J-A09</t>
         </is>
       </c>
       <c r="C612" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>📝 TERRY D HOWELL, MD, PC</t>
+          <t>📝 *NOVAMEDICA, PLLC</t>
         </is>
       </c>
       <c r="E612" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Oct 20</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Aug 14</t>
         </is>
       </c>
       <c r="F612" s="3" t="inlineStr">
@@ -40596,7 +40592,7 @@
       </c>
       <c r="G612" s="3" t="inlineStr">
         <is>
-          <t>4e57efb6-1ae9-4171-ac14-4be29705805c</t>
+          <t>d2a011ae-fad5-4195-a59b-93376dd15321</t>
         </is>
       </c>
       <c r="H612" s="3" t="inlineStr">
@@ -40614,12 +40610,12 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>Saline</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>401 N ANN ARBOR ST STE D, SALINE, MI, 48176</t>
+          <t>20331 FARMINGTON RD STE 103, LIVONIA, MI, 48152</t>
         </is>
       </c>
       <c r="M612" s="4" t="n"/>
@@ -40637,26 +40633,26 @@
         </is>
       </c>
       <c r="C613" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>📝 Trinity Health IHA Medical Group, Primary Care - Ann Arbor</t>
+          <t>📝 TERRY D HOWELL, MD, PC</t>
         </is>
       </c>
       <c r="E613" s="4" t="inlineStr">
         <is>
-          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Sep 16</t>
+          <t>Tier 2 ortho · last check-in Oct 20</t>
         </is>
       </c>
       <c r="F613" s="3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G613" s="3" t="inlineStr">
         <is>
-          <t>41bbf717-a150-4c1a-b236-ebab1366b8aa</t>
+          <t>4e57efb6-1ae9-4171-ac14-4be29705805c</t>
         </is>
       </c>
       <c r="H613" s="3" t="inlineStr">
@@ -40674,12 +40670,12 @@
       </c>
       <c r="K613" s="3" t="inlineStr">
         <is>
-          <t>Ypsilanti</t>
+          <t>Saline</t>
         </is>
       </c>
       <c r="L613" s="4" t="inlineStr">
         <is>
-          <t>5361 McAuley Dr, Ypsilanti, Michigan, 48197</t>
+          <t>401 N ANN ARBOR ST STE D, SALINE, MI, 48176</t>
         </is>
       </c>
       <c r="M613" s="4" t="n"/>
@@ -40697,26 +40693,26 @@
         </is>
       </c>
       <c r="C614" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>📝 Medical Associates PC</t>
+          <t>📝 Trinity Health IHA Medical Group, Primary Care - Ann Arbor</t>
         </is>
       </c>
       <c r="E614" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jun 29</t>
+          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Sep 16</t>
         </is>
       </c>
       <c r="F614" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>ed5b6926-cd2d-40c7-b534-97499a80ee08</t>
+          <t>41bbf717-a150-4c1a-b236-ebab1366b8aa</t>
         </is>
       </c>
       <c r="H614" s="3" t="inlineStr">
@@ -40739,7 +40735,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>428 S Grove St, Ypsilanti, Michigan, 48198</t>
+          <t>5361 McAuley Dr, Ypsilanti, Michigan, 48197</t>
         </is>
       </c>
       <c r="M614" s="4" t="n"/>
@@ -40757,26 +40753,26 @@
         </is>
       </c>
       <c r="C615" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>📝 BEAUMONT FAMILY MEDICINE BELLEVILLE</t>
+          <t>📝 Medical Associates PC</t>
         </is>
       </c>
       <c r="E615" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 6</t>
+          <t>Prospect · last check-in Jun 29</t>
         </is>
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>61a031d7-889d-4b90-8391-8647f4be87ec</t>
+          <t>ed5b6926-cd2d-40c7-b534-97499a80ee08</t>
         </is>
       </c>
       <c r="H615" s="3" t="inlineStr">
@@ -40790,16 +40786,16 @@
         </is>
       </c>
       <c r="J615" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K615" s="3" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Ypsilanti</t>
         </is>
       </c>
       <c r="L615" s="4" t="inlineStr">
         <is>
-          <t>201 3RD ST STE 200, BELLEVILLE, Michigan</t>
+          <t>428 S Grove St, Ypsilanti, Michigan, 48198</t>
         </is>
       </c>
       <c r="M615" s="4" t="n"/>
@@ -40817,16 +40813,16 @@
         </is>
       </c>
       <c r="C616" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>📝 Trinity Health IHA Medical Group Primary Care - Canton</t>
+          <t>📝 BEAUMONT FAMILY MEDICINE BELLEVILLE</t>
         </is>
       </c>
       <c r="E616" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 25</t>
+          <t>Tier 1 producer · last check-in Oct 6</t>
         </is>
       </c>
       <c r="F616" s="3" t="inlineStr">
@@ -40836,7 +40832,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>25a91d51-ca80-40cd-88ea-8b37beaa2ea8</t>
+          <t>61a031d7-889d-4b90-8391-8647f4be87ec</t>
         </is>
       </c>
       <c r="H616" s="3" t="inlineStr">
@@ -40854,12 +40850,12 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>1600 S Canton Center Road, Suite 200, CANTON, Michigan, 48188</t>
+          <t>201 3RD ST STE 200, BELLEVILLE, Michigan</t>
         </is>
       </c>
       <c r="M616" s="4" t="n"/>
@@ -40877,16 +40873,16 @@
         </is>
       </c>
       <c r="C617" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>UofM Canton Health Center Adult Medicine &amp; Pediatrics</t>
+          <t>📝 Trinity Health IHA Medical Group Primary Care - Canton</t>
         </is>
       </c>
       <c r="E617" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 22</t>
+          <t>Tier 1 producer · last check-in Aug 25</t>
         </is>
       </c>
       <c r="F617" s="3" t="inlineStr">
@@ -40896,17 +40892,17 @@
       </c>
       <c r="G617" s="3" t="inlineStr">
         <is>
-          <t>23783a21-557a-406e-a930-d9d15e509c4d</t>
+          <t>25a91d51-ca80-40cd-88ea-8b37beaa2ea8</t>
         </is>
       </c>
       <c r="H617" s="3" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I617" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J617" s="3" t="n">
@@ -40919,7 +40915,7 @@
       </c>
       <c r="L617" s="4" t="inlineStr">
         <is>
-          <t>1051 North Canton Center Road, Canton, MI 48187</t>
+          <t>1600 S Canton Center Road, Suite 200, CANTON, Michigan, 48188</t>
         </is>
       </c>
       <c r="M617" s="4" t="n"/>
@@ -40937,16 +40933,16 @@
         </is>
       </c>
       <c r="C618" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>📝 Corwell health orthopedics Canton</t>
+          <t>UofM Canton Health Center Adult Medicine &amp; Pediatrics</t>
         </is>
       </c>
       <c r="E618" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Sep 22</t>
         </is>
       </c>
       <c r="F618" s="3" t="inlineStr">
@@ -40956,17 +40952,17 @@
       </c>
       <c r="G618" s="3" t="inlineStr">
         <is>
-          <t>48d727c6-d942-4dbb-b457-0839ac8e1b68</t>
+          <t>23783a21-557a-406e-a930-d9d15e509c4d</t>
         </is>
       </c>
       <c r="H618" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="I618" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J618" s="3" t="n">
@@ -40979,7 +40975,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2050 North Haggerty Road, Canton, Michigan, 48187</t>
+          <t>1051 North Canton Center Road, Canton, MI 48187</t>
         </is>
       </c>
       <c r="M618" s="4" t="n"/>
@@ -40997,16 +40993,16 @@
         </is>
       </c>
       <c r="C619" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>📝 Park Medical Centers - Canton</t>
+          <t>📝 Corwell health orthopedics Canton</t>
         </is>
       </c>
       <c r="E619" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 24</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F619" s="3" t="inlineStr">
@@ -41016,12 +41012,12 @@
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>047f1f57-d796-4b0d-b2d0-b5d576ad50ea</t>
+          <t>48d727c6-d942-4dbb-b457-0839ac8e1b68</t>
         </is>
       </c>
       <c r="H619" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I619" s="3" t="inlineStr">
@@ -41030,7 +41026,7 @@
         </is>
       </c>
       <c r="J619" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K619" s="3" t="inlineStr">
         <is>
@@ -41039,7 +41035,7 @@
       </c>
       <c r="L619" s="4" t="inlineStr">
         <is>
-          <t>8532 N CANTON CENTER RD, CANTON, MI, 48187</t>
+          <t>2050 North Haggerty Road, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M619" s="4" t="n"/>
@@ -41057,16 +41053,16 @@
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>📝 A1 Family Medicine</t>
+          <t>📝 Park Medical Centers - Canton</t>
         </is>
       </c>
       <c r="E620" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 1</t>
+          <t>Tier 1 producer · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F620" s="3" t="inlineStr">
@@ -41076,7 +41072,7 @@
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>b1a9167c-0bb6-47bd-b50a-ff18a973875f</t>
+          <t>047f1f57-d796-4b0d-b2d0-b5d576ad50ea</t>
         </is>
       </c>
       <c r="H620" s="3" t="inlineStr">
@@ -41090,7 +41086,7 @@
         </is>
       </c>
       <c r="J620" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
@@ -41099,7 +41095,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2050 N Haggerty Rd, Canton, Michigan, 48187</t>
+          <t>8532 N CANTON CENTER RD, CANTON, MI, 48187</t>
         </is>
       </c>
       <c r="M620" s="4" t="n"/>
@@ -41117,11 +41113,11 @@
         </is>
       </c>
       <c r="C621" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>📝 CANTON FAMILY HEALTH LLC</t>
+          <t>📝 A1 Family Medicine</t>
         </is>
       </c>
       <c r="E621" s="4" t="inlineStr">
@@ -41136,7 +41132,7 @@
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>3acfe2ff-d550-4785-99aa-a1ea91ef7da4</t>
+          <t>b1a9167c-0bb6-47bd-b50a-ff18a973875f</t>
         </is>
       </c>
       <c r="H621" s="3" t="inlineStr">
@@ -41150,7 +41146,7 @@
         </is>
       </c>
       <c r="J621" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K621" s="3" t="inlineStr">
         <is>
@@ -41159,7 +41155,7 @@
       </c>
       <c r="L621" s="4" t="inlineStr">
         <is>
-          <t>6300 N HAGGERTY RD STE 220, CANTON, MI, 48187</t>
+          <t>2050 N Haggerty Rd, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M621" s="4" t="n"/>
@@ -41168,35 +41164,35 @@
     <row r="622">
       <c r="A622" s="3" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
         <is>
-          <t>J-A02</t>
+          <t>J-A11</t>
         </is>
       </c>
       <c r="C622" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>📝 WEST OAKLAND INTERNISTS</t>
+          <t>📝 CANTON FAMILY HEALTH LLC</t>
         </is>
       </c>
       <c r="E622" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Oct 7</t>
+          <t>Tier 1 producer · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F622" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>b9dc6f52-5aa2-459e-98a8-79b4da67dc8a</t>
+          <t>3acfe2ff-d550-4785-99aa-a1ea91ef7da4</t>
         </is>
       </c>
       <c r="H622" s="3" t="inlineStr">
@@ -41210,16 +41206,16 @@
         </is>
       </c>
       <c r="J622" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>44000 W 12 MILE RD STE 200, NOVI, MI, 48377</t>
+          <t>6300 N HAGGERTY RD STE 220, CANTON, MI, 48187</t>
         </is>
       </c>
       <c r="M622" s="4" t="n"/>
@@ -41237,11 +41233,11 @@
         </is>
       </c>
       <c r="C623" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>📝 Corewell Health Family Care of Novi</t>
+          <t>📝 WEST OAKLAND INTERNISTS</t>
         </is>
       </c>
       <c r="E623" s="4" t="inlineStr">
@@ -41256,7 +41252,7 @@
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>74e299c3-f9b1-4d54-8e8d-b63af23ba7fd</t>
+          <t>b9dc6f52-5aa2-459e-98a8-79b4da67dc8a</t>
         </is>
       </c>
       <c r="H623" s="3" t="inlineStr">
@@ -41279,7 +41275,7 @@
       </c>
       <c r="L623" s="4" t="inlineStr">
         <is>
-          <t>44130 W 12 MILE RD, NOVI, MI, 48377</t>
+          <t>44000 W 12 MILE RD STE 200, NOVI, MI, 48377</t>
         </is>
       </c>
       <c r="M623" s="4" t="n"/>
@@ -41297,16 +41293,16 @@
         </is>
       </c>
       <c r="C624" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>📝 Novi Medicine</t>
+          <t>📝 Corewell Health Family Care of Novi</t>
         </is>
       </c>
       <c r="E624" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Sep 29</t>
+          <t>Tier 2 ortho · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F624" s="3" t="inlineStr">
@@ -41316,7 +41312,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>bd0ee186-9de1-49f1-b6f7-85fc538efd3b</t>
+          <t>74e299c3-f9b1-4d54-8e8d-b63af23ba7fd</t>
         </is>
       </c>
       <c r="H624" s="3" t="inlineStr">
@@ -41339,7 +41335,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>39475 LEWIS DR STE 150, NOVI, MI, 48377</t>
+          <t>44130 W 12 MILE RD, NOVI, MI, 48377</t>
         </is>
       </c>
       <c r="M624" s="4" t="n"/>
@@ -41357,31 +41353,31 @@
         </is>
       </c>
       <c r="C625" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>📝 Premier Medicine Medical Center - Livonia</t>
+          <t>📝 Novi Medicine</t>
         </is>
       </c>
       <c r="E625" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 17</t>
+          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F625" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G625" s="3" t="inlineStr">
         <is>
-          <t>13842362-6701-47f3-95cc-140ea17bd264</t>
+          <t>bd0ee186-9de1-49f1-b6f7-85fc538efd3b</t>
         </is>
       </c>
       <c r="H625" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I625" s="3" t="inlineStr">
@@ -41390,16 +41386,16 @@
         </is>
       </c>
       <c r="J625" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K625" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L625" s="4" t="inlineStr">
         <is>
-          <t>20290 Middlebelt Rd, Livonia, Michigan, 48152</t>
+          <t>39475 LEWIS DR STE 150, NOVI, MI, 48377</t>
         </is>
       </c>
       <c r="M625" s="4" t="n"/>
@@ -41417,31 +41413,31 @@
         </is>
       </c>
       <c r="C626" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>📝 Michigan Orthopedic Surgeons- Southfield</t>
+          <t>📝 Premier Medicine Medical Center - Livonia</t>
         </is>
       </c>
       <c r="E626" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 27</t>
+          <t>Tier 1 producer · last check-in Sep 17</t>
         </is>
       </c>
       <c r="F626" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G626" s="3" t="inlineStr">
         <is>
-          <t>e1c8dbbf-56d1-41b9-82e4-7fa1950cb943</t>
+          <t>13842362-6701-47f3-95cc-140ea17bd264</t>
         </is>
       </c>
       <c r="H626" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I626" s="3" t="inlineStr">
@@ -41450,16 +41446,16 @@
         </is>
       </c>
       <c r="J626" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>26025 Lahser Rd, Southfield, Michigan, 48033</t>
+          <t>20290 Middlebelt Rd, Livonia, Michigan, 48152</t>
         </is>
       </c>
       <c r="M626" s="4" t="n"/>
@@ -41477,26 +41473,26 @@
         </is>
       </c>
       <c r="C627" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>📝 Roberts Orthopedic Services</t>
+          <t>📝 Michigan Orthopedic Surgeons- Southfield</t>
         </is>
       </c>
       <c r="E627" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 8</t>
+          <t>Prospect · last check-in Jul 27</t>
         </is>
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr">
         <is>
-          <t>680822f2-58d4-4f67-b09b-01ccd6f95892</t>
+          <t>e1c8dbbf-56d1-41b9-82e4-7fa1950cb943</t>
         </is>
       </c>
       <c r="H627" s="3" t="inlineStr">
@@ -41510,7 +41506,7 @@
         </is>
       </c>
       <c r="J627" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K627" s="3" t="inlineStr">
         <is>
@@ -41519,7 +41515,7 @@
       </c>
       <c r="L627" s="4" t="inlineStr">
         <is>
-          <t>27207 Lahser Rd, Southfield, Michigan, 48034</t>
+          <t>26025 Lahser Rd, Southfield, Michigan, 48033</t>
         </is>
       </c>
       <c r="M627" s="4" t="n"/>
@@ -41537,26 +41533,26 @@
         </is>
       </c>
       <c r="C628" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>📝 DEDICATED SENIOR MEDICAL CENTER - Southfield</t>
+          <t>📝 Roberts Orthopedic Services</t>
         </is>
       </c>
       <c r="E628" s="4" t="inlineStr">
         <is>
-          <t>Tier 3 · last check-in Sep 8</t>
+          <t>Tier 1 producer · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F628" s="3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G628" s="3" t="inlineStr">
         <is>
-          <t>12deaf83-0f5e-4bd5-bf07-a4026935ffd1</t>
+          <t>680822f2-58d4-4f67-b09b-01ccd6f95892</t>
         </is>
       </c>
       <c r="H628" s="3" t="inlineStr">
@@ -41570,7 +41566,7 @@
         </is>
       </c>
       <c r="J628" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
@@ -41579,7 +41575,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>21816 w 11 mile rd, Southfield, Michigan, 48076</t>
+          <t>27207 Lahser Rd, Southfield, Michigan, 48034</t>
         </is>
       </c>
       <c r="M628" s="4" t="n"/>
@@ -41597,11 +41593,11 @@
         </is>
       </c>
       <c r="C629" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>📝 SOUTHFIELD URGENT CARE</t>
+          <t>📝 DEDICATED SENIOR MEDICAL CENTER - Southfield</t>
         </is>
       </c>
       <c r="E629" s="4" t="inlineStr">
@@ -41616,12 +41612,12 @@
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>f8db03fe-3188-4a31-b4ee-6010086c7552</t>
+          <t>12deaf83-0f5e-4bd5-bf07-a4026935ffd1</t>
         </is>
       </c>
       <c r="H629" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I629" s="3" t="inlineStr">
@@ -41639,7 +41635,7 @@
       </c>
       <c r="L629" s="4" t="inlineStr">
         <is>
-          <t>23832 SOUTHFIELD RD STE 1, SOUTHFIELD, Michigan</t>
+          <t>21816 w 11 mile rd, Southfield, Michigan, 48076</t>
         </is>
       </c>
       <c r="M629" s="4" t="n"/>
@@ -41657,31 +41653,31 @@
         </is>
       </c>
       <c r="C630" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>📝 Core Institute/Henry Ford Motor City Orthopedics &amp; PT- Southfield</t>
+          <t>📝 SOUTHFIELD URGENT CARE</t>
         </is>
       </c>
       <c r="E630" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Sep 23</t>
+          <t>Tier 3 · last check-in Sep 8</t>
         </is>
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>b2290856-de23-4322-aabc-b2436529feac</t>
+          <t>f8db03fe-3188-4a31-b4ee-6010086c7552</t>
         </is>
       </c>
       <c r="H630" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I630" s="3" t="inlineStr">
@@ -41690,7 +41686,7 @@
         </is>
       </c>
       <c r="J630" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
@@ -41699,7 +41695,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>22250 Providence Drive, ste 401, Southfield, Michigan, 48075</t>
+          <t>23832 SOUTHFIELD RD STE 1, SOUTHFIELD, Michigan</t>
         </is>
       </c>
       <c r="M630" s="4" t="n"/>
@@ -41717,31 +41713,31 @@
         </is>
       </c>
       <c r="C631" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>📝 ACADEMIC INTERNAL MEDICINE SPECIALISTS</t>
+          <t>📝 Core Institute/Henry Ford Motor City Orthopedics &amp; PT- Southfield</t>
         </is>
       </c>
       <c r="E631" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Sep 23</t>
         </is>
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>24230075-46f5-44cf-bd8f-deb5f276aa99</t>
+          <t>b2290856-de23-4322-aabc-b2436529feac</t>
         </is>
       </c>
       <c r="H631" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I631" s="3" t="inlineStr">
@@ -41750,7 +41746,7 @@
         </is>
       </c>
       <c r="J631" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K631" s="3" t="inlineStr">
         <is>
@@ -41759,7 +41755,7 @@
       </c>
       <c r="L631" s="4" t="inlineStr">
         <is>
-          <t>22250 PROVIDENCE DR STE 301, SOUTHFIELD, Michigan, 48075</t>
+          <t>22250 Providence Drive, ste 401, Southfield, Michigan, 48075</t>
         </is>
       </c>
       <c r="M631" s="4" t="n"/>
@@ -41773,20 +41769,20 @@
       </c>
       <c r="B632" s="3" t="inlineStr">
         <is>
-          <t>J-A03</t>
+          <t>J-A02</t>
         </is>
       </c>
       <c r="C632" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Healthcare</t>
+          <t>📝 ACADEMIC INTERNAL MEDICINE SPECIALISTS</t>
         </is>
       </c>
       <c r="E632" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Jun 22</t>
+          <t>Tier 2 ortho · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F632" s="3" t="inlineStr">
@@ -41796,17 +41792,17 @@
       </c>
       <c r="G632" s="3" t="inlineStr">
         <is>
-          <t>5a20e303-4955-44e6-b500-198952d6dc85</t>
+          <t>24230075-46f5-44cf-bd8f-deb5f276aa99</t>
         </is>
       </c>
       <c r="H632" s="3" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I632" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J632" s="3" t="n">
@@ -41814,12 +41810,12 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>Sterling Heights</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>33464 Schoenherr Road, Sterling Heights, MI 48312</t>
+          <t>22250 PROVIDENCE DR STE 301, SOUTHFIELD, Michigan, 48075</t>
         </is>
       </c>
       <c r="M632" s="4" t="n"/>
@@ -41837,16 +41833,16 @@
         </is>
       </c>
       <c r="C633" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>📝 Michigan Primary Care - Eastpointe</t>
+          <t>Dynamic Healthcare</t>
         </is>
       </c>
       <c r="E633" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 10</t>
+          <t>Tier 2 ortho · last check-in Jun 22</t>
         </is>
       </c>
       <c r="F633" s="3" t="inlineStr">
@@ -41856,17 +41852,17 @@
       </c>
       <c r="G633" s="3" t="inlineStr">
         <is>
-          <t>4328f444-1a86-4fbb-9849-e8a159cce3e2</t>
+          <t>5a20e303-4955-44e6-b500-198952d6dc85</t>
         </is>
       </c>
       <c r="H633" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PCP / IM / FM</t>
         </is>
       </c>
       <c r="I633" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J633" s="3" t="n">
@@ -41874,12 +41870,12 @@
       </c>
       <c r="K633" s="3" t="inlineStr">
         <is>
-          <t>Eastpointe</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="L633" s="4" t="inlineStr">
         <is>
-          <t>17000 E 10 Mile Rd, Eastpointe, MI, 48021</t>
+          <t>33464 Schoenherr Road, Sterling Heights, MI 48312</t>
         </is>
       </c>
       <c r="M633" s="4" t="n"/>
@@ -41897,26 +41893,26 @@
         </is>
       </c>
       <c r="C634" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>📝 Eastpointe Family Physicians</t>
+          <t>📝 Michigan Primary Care - Eastpointe</t>
         </is>
       </c>
       <c r="E634" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 2 ortho · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F634" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G634" s="3" t="inlineStr">
         <is>
-          <t>1578685921</t>
+          <t>4328f444-1a86-4fbb-9849-e8a159cce3e2</t>
         </is>
       </c>
       <c r="H634" s="3" t="inlineStr">
@@ -41930,7 +41926,7 @@
         </is>
       </c>
       <c r="J634" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
@@ -41939,7 +41935,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>24901 Kelly Rd, Eastpointe, MI, 48021</t>
+          <t>17000 E 10 Mile Rd, Eastpointe, MI, 48021</t>
         </is>
       </c>
       <c r="M634" s="4" t="n"/>
@@ -41957,11 +41953,11 @@
         </is>
       </c>
       <c r="C635" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>📝 QuickDoc Urgent Care</t>
+          <t>📝 Eastpointe Family Physicians</t>
         </is>
       </c>
       <c r="E635" s="4" t="inlineStr">
@@ -41976,12 +41972,12 @@
       </c>
       <c r="G635" s="3" t="inlineStr">
         <is>
-          <t>20e3535a-e9f3-4760-9cd8-6e86789495da</t>
+          <t>1578685921</t>
         </is>
       </c>
       <c r="H635" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I635" s="3" t="inlineStr">
@@ -41990,7 +41986,7 @@
         </is>
       </c>
       <c r="J635" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K635" s="3" t="inlineStr">
         <is>
@@ -41999,7 +41995,7 @@
       </c>
       <c r="L635" s="4" t="inlineStr">
         <is>
-          <t>19070 East 10 Mile Road, Eastpointe, Michigan, 48021</t>
+          <t>24901 Kelly Rd, Eastpointe, MI, 48021</t>
         </is>
       </c>
       <c r="M635" s="4" t="n"/>
@@ -42017,31 +42013,31 @@
         </is>
       </c>
       <c r="C636" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>📝 Tri County Neurology</t>
+          <t>📝 QuickDoc Urgent Care</t>
         </is>
       </c>
       <c r="E636" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 10</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F636" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G636" s="3" t="inlineStr">
         <is>
-          <t>3d10a23f-49c8-4b30-b87f-ae7465e0f588</t>
+          <t>20e3535a-e9f3-4760-9cd8-6e86789495da</t>
         </is>
       </c>
       <c r="H636" s="3" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I636" s="3" t="inlineStr">
@@ -42050,7 +42046,7 @@
         </is>
       </c>
       <c r="J636" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
@@ -42059,7 +42055,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>18161 E 8 Mile Rd, Eastpointe, Michigan, 48021</t>
+          <t>19070 East 10 Mile Road, Eastpointe, Michigan, 48021</t>
         </is>
       </c>
       <c r="M636" s="4" t="n"/>
@@ -42077,31 +42073,31 @@
         </is>
       </c>
       <c r="C637" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>📝 Park Medical Center (Medicaid)</t>
+          <t>📝 Tri County Neurology</t>
         </is>
       </c>
       <c r="E637" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Oct 5</t>
+          <t>Tier 2 ortho · last check-in Sep 10</t>
         </is>
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G637" s="3" t="inlineStr">
         <is>
-          <t>c4cc522a-15ee-4dcb-8312-cc7b7efdf995</t>
+          <t>3d10a23f-49c8-4b30-b87f-ae7465e0f588</t>
         </is>
       </c>
       <c r="H637" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="I637" s="3" t="inlineStr">
@@ -42110,16 +42106,16 @@
         </is>
       </c>
       <c r="J637" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K637" s="3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Eastpointe</t>
         </is>
       </c>
       <c r="L637" s="4" t="inlineStr">
         <is>
-          <t>12871 East Jefferson Avenue, Detroit, Michigan, 48215</t>
+          <t>18161 E 8 Mile Rd, Eastpointe, Michigan, 48021</t>
         </is>
       </c>
       <c r="M637" s="4" t="n"/>
@@ -42137,16 +42133,16 @@
         </is>
       </c>
       <c r="C638" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>📝 Wayne state Internal Medicine</t>
+          <t>📝 Park Medical Center (Medicaid)</t>
         </is>
       </c>
       <c r="E638" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 5</t>
+          <t>Tier 1 producer · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F638" s="3" t="inlineStr">
@@ -42156,7 +42152,7 @@
       </c>
       <c r="G638" s="3" t="inlineStr">
         <is>
-          <t>39af8a2b-3c99-4502-805c-10e5627efc9d</t>
+          <t>c4cc522a-15ee-4dcb-8312-cc7b7efdf995</t>
         </is>
       </c>
       <c r="H638" s="3" t="inlineStr">
@@ -42179,7 +42175,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>4201 St Antoine, Detroit, Michigan, 48201</t>
+          <t>12871 East Jefferson Avenue, Detroit, Michigan, 48215</t>
         </is>
       </c>
       <c r="M638" s="4" t="n"/>
@@ -42197,40 +42193,40 @@
         </is>
       </c>
       <c r="C639" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>UNIVERSITY PAIN CLINIC ASSOCIATES</t>
+          <t>📝 Wayne state Internal Medicine</t>
         </is>
       </c>
       <c r="E639" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Feb 24</t>
+          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Oct 5</t>
         </is>
       </c>
       <c r="F639" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G639" s="3" t="inlineStr">
         <is>
-          <t>a3d9f2e6-b3cf-4fda-87e5-1cbd899fa7b6</t>
+          <t>39af8a2b-3c99-4502-805c-10e5627efc9d</t>
         </is>
       </c>
       <c r="H639" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I639" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J639" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K639" s="3" t="inlineStr">
         <is>
@@ -42239,7 +42235,7 @@
       </c>
       <c r="L639" s="4" t="inlineStr">
         <is>
-          <t>4160 John R St, Ste 522, Detroit, MI 48201</t>
+          <t>4201 St Antoine, Detroit, Michigan, 48201</t>
         </is>
       </c>
       <c r="M639" s="4" t="n"/>
@@ -42257,36 +42253,36 @@
         </is>
       </c>
       <c r="C640" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>📝 Premier Medicine Primary and Urgent Care</t>
+          <t>UNIVERSITY PAIN CLINIC ASSOCIATES</t>
         </is>
       </c>
       <c r="E640" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 14</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Feb 24</t>
         </is>
       </c>
       <c r="F640" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G640" s="3" t="inlineStr">
         <is>
-          <t>9288d919-ada8-45ca-a122-9e5065f74980</t>
+          <t>a3d9f2e6-b3cf-4fda-87e5-1cbd899fa7b6</t>
         </is>
       </c>
       <c r="H640" s="3" t="inlineStr">
         <is>
-          <t>Urgent Care</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I640" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
         </is>
       </c>
       <c r="J640" s="3" t="n">
@@ -42294,12 +42290,12 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>9550 Dix Ave, Dearborn, Michigan, 48120</t>
+          <t>4160 John R St, Ste 522, Detroit, MI 48201</t>
         </is>
       </c>
       <c r="M640" s="4" t="n"/>
@@ -42317,16 +42313,16 @@
         </is>
       </c>
       <c r="C641" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>📝 Corwell health internal medicine, Dearborn</t>
+          <t>📝 Medical center (HMC)Urgent Care</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 14</t>
+          <t>Prospect · last check-in Jul 17</t>
         </is>
       </c>
       <c r="F641" s="3" t="inlineStr">
@@ -42336,12 +42332,12 @@
       </c>
       <c r="G641" s="3" t="inlineStr">
         <is>
-          <t>1881654705</t>
+          <t>a9e468b9-b41a-4205-a0b3-bbf1f8829426</t>
         </is>
       </c>
       <c r="H641" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I641" s="3" t="inlineStr">
@@ -42359,7 +42355,7 @@
       </c>
       <c r="L641" s="4" t="inlineStr">
         <is>
-          <t>4700 Schaefer Rd, Suite 240, Dearborn, MI, 481263698</t>
+          <t>7542 Wyoming Avenue, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M641" s="4" t="n"/>
@@ -42373,20 +42369,20 @@
       </c>
       <c r="B642" s="3" t="inlineStr">
         <is>
-          <t>J-A04</t>
+          <t>J-A03</t>
         </is>
       </c>
       <c r="C642" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>📝 Henry Ford urgent care Livonia</t>
+          <t>📝 Premier Medicine Primary and Urgent Care</t>
         </is>
       </c>
       <c r="E642" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 18</t>
+          <t>Prospect · last check-in Jul 14</t>
         </is>
       </c>
       <c r="F642" s="3" t="inlineStr">
@@ -42396,7 +42392,7 @@
       </c>
       <c r="G642" s="3" t="inlineStr">
         <is>
-          <t>3e9f6915-4170-47c8-892b-d54aead4f00f</t>
+          <t>9288d919-ada8-45ca-a122-9e5065f74980</t>
         </is>
       </c>
       <c r="H642" s="3" t="inlineStr">
@@ -42414,12 +42410,12 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>29531 Plymouth Road, Livonia, Michigan, 48150</t>
+          <t>9550 Dix Ave, Dearborn, Michigan, 48120</t>
         </is>
       </c>
       <c r="M642" s="4" t="n"/>
@@ -42437,11 +42433,11 @@
         </is>
       </c>
       <c r="C643" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>📝 The Joint Chiropractic - Livonia</t>
+          <t>📝 Henry Ford urgent care Livonia</t>
         </is>
       </c>
       <c r="E643" s="4" t="inlineStr">
@@ -42456,12 +42452,12 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>fbf2356b-694f-4b80-a662-1d1e86c727d7</t>
+          <t>3e9f6915-4170-47c8-892b-d54aead4f00f</t>
         </is>
       </c>
       <c r="H643" s="3" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Urgent Care</t>
         </is>
       </c>
       <c r="I643" s="3" t="inlineStr">
@@ -42479,7 +42475,7 @@
       </c>
       <c r="L643" s="4" t="inlineStr">
         <is>
-          <t>11027 Middlebelt Rd, Livonia, Michigan, 48150</t>
+          <t>29531 Plymouth Road, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M643" s="4" t="n"/>
@@ -42497,7 +42493,7 @@
         </is>
       </c>
       <c r="C644" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D644" s="4" t="inlineStr">
         <is>
@@ -42557,7 +42553,7 @@
         </is>
       </c>
       <c r="C645" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D645" s="4" t="inlineStr">
         <is>
@@ -42617,7 +42613,7 @@
         </is>
       </c>
       <c r="C646" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D646" s="4" t="inlineStr">
         <is>
@@ -42677,7 +42673,7 @@
         </is>
       </c>
       <c r="C647" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
@@ -42737,7 +42733,7 @@
         </is>
       </c>
       <c r="C648" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D648" s="4" t="inlineStr">
         <is>
@@ -42797,7 +42793,7 @@
         </is>
       </c>
       <c r="C649" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
@@ -42857,11 +42853,11 @@
         </is>
       </c>
       <c r="C650" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>📝 Dearborn medical and geriatric center</t>
+          <t>📝 DR VIJAYA CHALLA, MD, PC</t>
         </is>
       </c>
       <c r="E650" s="4" t="inlineStr">
@@ -42876,7 +42872,7 @@
       </c>
       <c r="G650" s="3" t="inlineStr">
         <is>
-          <t>e8faaf5d-bdac-4971-9f83-bd77a1c37b96</t>
+          <t>5cce6822-d3c7-400b-a3ee-0b6788d7b144</t>
         </is>
       </c>
       <c r="H650" s="3" t="inlineStr">
@@ -42899,7 +42895,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>24100 Oxford Street, Dearborn, Michigan, 48124</t>
+          <t>24604 MICHIGAN AVE STE 100, DEARBORN, MI, 48124</t>
         </is>
       </c>
       <c r="M650" s="4" t="n"/>
@@ -42917,11 +42913,11 @@
         </is>
       </c>
       <c r="C651" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>📝 GREENFIELD MEDICAL CENTER OF DEARBORN, PC</t>
+          <t>📝 Dearborn medical and geriatric center</t>
         </is>
       </c>
       <c r="E651" s="4" t="inlineStr">
@@ -42936,12 +42932,12 @@
       </c>
       <c r="G651" s="3" t="inlineStr">
         <is>
-          <t>7e17dd91-d956-482b-a527-df4bc27f78c0</t>
+          <t>e8faaf5d-bdac-4971-9f83-bd77a1c37b96</t>
         </is>
       </c>
       <c r="H651" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I651" s="3" t="inlineStr">
@@ -42959,7 +42955,7 @@
       </c>
       <c r="L651" s="4" t="inlineStr">
         <is>
-          <t>5220 OAKMAN BLVD, DEARBORN, Michigan, 48126</t>
+          <t>24100 Oxford Street, Dearborn, Michigan, 48124</t>
         </is>
       </c>
       <c r="M651" s="4" t="n"/>
@@ -42973,20 +42969,20 @@
       </c>
       <c r="B652" s="3" t="inlineStr">
         <is>
-          <t>J-A12</t>
+          <t>J-A04</t>
         </is>
       </c>
       <c r="C652" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>True Health Chiropractic</t>
+          <t>📝 GREENFIELD MEDICAL CENTER OF DEARBORN, PC</t>
         </is>
       </c>
       <c r="E652" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 18</t>
+          <t>Prospect · last check-in Aug 24</t>
         </is>
       </c>
       <c r="F652" s="3" t="inlineStr">
@@ -42996,12 +42992,12 @@
       </c>
       <c r="G652" s="3" t="inlineStr">
         <is>
-          <t>bb1e8257-48ba-4510-ac85-f82c85996bdf</t>
+          <t>7e17dd91-d956-482b-a527-df4bc27f78c0</t>
         </is>
       </c>
       <c r="H652" s="3" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I652" s="3" t="inlineStr">
@@ -43014,12 +43010,12 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>Livonia</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>28404 Five Mile Rd, Livonia, Michigan, 48154</t>
+          <t>5220 OAKMAN BLVD, DEARBORN, Michigan, 48126</t>
         </is>
       </c>
       <c r="M652" s="4" t="n"/>
@@ -43037,16 +43033,16 @@
         </is>
       </c>
       <c r="C653" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>True Health Chiropractic</t>
         </is>
       </c>
       <c r="E653" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 10</t>
+          <t>Prospect · last check-in Aug 18</t>
         </is>
       </c>
       <c r="F653" s="3" t="inlineStr">
@@ -43056,12 +43052,12 @@
       </c>
       <c r="G653" s="3" t="inlineStr">
         <is>
-          <t>be40181f-bcb8-4cac-ae76-ab9ba0311605</t>
+          <t>bb1e8257-48ba-4510-ac85-f82c85996bdf</t>
         </is>
       </c>
       <c r="H653" s="3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I653" s="3" t="inlineStr">
@@ -43079,7 +43075,7 @@
       </c>
       <c r="L653" s="4" t="inlineStr">
         <is>
-          <t>29539 Plymouth Rd, Livonia, Michigan, 48150</t>
+          <t>28404 Five Mile Rd, Livonia, Michigan, 48154</t>
         </is>
       </c>
       <c r="M653" s="4" t="n"/>
@@ -43097,31 +43093,31 @@
         </is>
       </c>
       <c r="C654" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="E654" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Aug 26</t>
+          <t>Prospect · last check-in Aug 10</t>
         </is>
       </c>
       <c r="F654" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G654" s="3" t="inlineStr">
         <is>
-          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
+          <t>be40181f-bcb8-4cac-ae76-ab9ba0311605</t>
         </is>
       </c>
       <c r="H654" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="I654" s="3" t="inlineStr">
@@ -43130,16 +43126,16 @@
         </is>
       </c>
       <c r="J654" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
+          <t>29539 Plymouth Rd, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M654" s="4" t="n"/>
@@ -43157,31 +43153,31 @@
         </is>
       </c>
       <c r="C655" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>📝 Schaefer Medical</t>
+          <t>📝 The Joint Chiropractic - Livonia</t>
         </is>
       </c>
       <c r="E655" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 24</t>
+          <t>Prospect · last check-in Aug 18</t>
         </is>
       </c>
       <c r="F655" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G655" s="3" t="inlineStr">
         <is>
-          <t>a5a464ab-73df-48e0-8f49-b80f6b89fc6b</t>
+          <t>fbf2356b-694f-4b80-a662-1d1e86c727d7</t>
         </is>
       </c>
       <c r="H655" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="I655" s="3" t="inlineStr">
@@ -43194,12 +43190,12 @@
       </c>
       <c r="K655" s="3" t="inlineStr">
         <is>
-          <t>Dearborn</t>
+          <t>Livonia</t>
         </is>
       </c>
       <c r="L655" s="4" t="inlineStr">
         <is>
-          <t>5245 Schaefer Rd, Dearborn, Michigan, 48126</t>
+          <t>11027 Middlebelt Rd, Livonia, Michigan, 48150</t>
         </is>
       </c>
       <c r="M655" s="4" t="n"/>
@@ -43217,31 +43213,31 @@
         </is>
       </c>
       <c r="C656" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>📝 Get well urgent care</t>
+          <t>📝 COREWELL HEALTH  INTERNAL MEDICINE DEARBORN</t>
         </is>
       </c>
       <c r="E656" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jul 17</t>
+          <t>Tier 1 producer · last check-in Aug 26</t>
         </is>
       </c>
       <c r="F656" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G656" s="3" t="inlineStr">
         <is>
-          <t>ce05f9ae-2ed1-4743-9131-ddf0d57e59eb</t>
+          <t>9d286e7b-6017-417c-8a6b-763fe942c9c2</t>
         </is>
       </c>
       <c r="H656" s="3" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I656" s="3" t="inlineStr">
@@ -43250,7 +43246,7 @@
         </is>
       </c>
       <c r="J656" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
@@ -43259,7 +43255,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>13244 W Warren Ave, Dearborn, Michigan, 48126</t>
+          <t>17000 Hubbard Dr, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M656" s="4" t="n"/>
@@ -43277,26 +43273,26 @@
         </is>
       </c>
       <c r="C657" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>📝 EASTBORN CLINIC, PLLC</t>
+          <t>📝 Schaefer Medical</t>
         </is>
       </c>
       <c r="E657" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Aug 10</t>
+          <t>Tier 2 ortho · last check-in Sep 24</t>
         </is>
       </c>
       <c r="F657" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G657" s="3" t="inlineStr">
         <is>
-          <t>a8634a8d-40a8-4c4d-84a9-ddf74b794be2</t>
+          <t>a5a464ab-73df-48e0-8f49-b80f6b89fc6b</t>
         </is>
       </c>
       <c r="H657" s="3" t="inlineStr">
@@ -43319,7 +43315,7 @@
       </c>
       <c r="L657" s="4" t="inlineStr">
         <is>
-          <t>7526 WYOMING ST STE 2, DEARBORN, MI, 48126</t>
+          <t>5245 Schaefer Rd, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M657" s="4" t="n"/>
@@ -43337,26 +43333,26 @@
         </is>
       </c>
       <c r="C658" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>📝 Medical center (HMC)Urgent Care</t>
+          <t>📝 Get well urgent care</t>
         </is>
       </c>
       <c r="E658" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 17</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Jul 17</t>
         </is>
       </c>
       <c r="F658" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G658" s="3" t="inlineStr">
         <is>
-          <t>a9e468b9-b41a-4205-a0b3-bbf1f8829426</t>
+          <t>ce05f9ae-2ed1-4743-9131-ddf0d57e59eb</t>
         </is>
       </c>
       <c r="H658" s="3" t="inlineStr">
@@ -43379,7 +43375,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>7542 Wyoming Avenue, Dearborn, Michigan, 48126</t>
+          <t>13244 W Warren Ave, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M658" s="4" t="n"/>
@@ -43397,11 +43393,11 @@
         </is>
       </c>
       <c r="C659" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>📝 APPOLINE MEDICAL CLINIC, PC</t>
+          <t>📝 EASTBORN CLINIC, PLLC</t>
         </is>
       </c>
       <c r="E659" s="4" t="inlineStr">
@@ -43416,12 +43412,12 @@
       </c>
       <c r="G659" s="3" t="inlineStr">
         <is>
-          <t>41d58a99-837a-4287-a726-afe3cda684c8</t>
+          <t>a8634a8d-40a8-4c4d-84a9-ddf74b794be2</t>
         </is>
       </c>
       <c r="H659" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I659" s="3" t="inlineStr">
@@ -43439,7 +43435,7 @@
       </c>
       <c r="L659" s="4" t="inlineStr">
         <is>
-          <t>8740 W Warren Ave, Dearborn, Michigan, 48126</t>
+          <t>7526 WYOMING ST STE 2, DEARBORN, MI, 48126</t>
         </is>
       </c>
       <c r="M659" s="4" t="n"/>
@@ -43457,31 +43453,31 @@
         </is>
       </c>
       <c r="C660" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D660" s="4" t="inlineStr">
         <is>
-          <t>📝 DOWN RIVER MEDICAL GROUP</t>
+          <t>📝 APPOLINE MEDICAL CLINIC, PC</t>
         </is>
       </c>
       <c r="E660" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Sep 21</t>
+          <t>Prospect · last check-in Aug 10</t>
         </is>
       </c>
       <c r="F660" s="3" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G660" s="3" t="inlineStr">
         <is>
-          <t>e88886fb-60ef-4d4e-8d44-578baf30fd25</t>
+          <t>41d58a99-837a-4287-a726-afe3cda684c8</t>
         </is>
       </c>
       <c r="H660" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Orthopedic</t>
         </is>
       </c>
       <c r="I660" s="3" t="inlineStr">
@@ -43490,16 +43486,16 @@
         </is>
       </c>
       <c r="J660" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>Wyandotte</t>
+          <t>Dearborn</t>
         </is>
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2300 Biddle Avenue, Wyandotte, Michigan, 48192</t>
+          <t>8740 W Warren Ave, Dearborn, Michigan, 48126</t>
         </is>
       </c>
       <c r="M660" s="4" t="n"/>
@@ -43517,16 +43513,16 @@
         </is>
       </c>
       <c r="C661" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D661" s="4" t="inlineStr">
         <is>
-          <t>Epic Medical Center</t>
+          <t>📝 DOWN RIVER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="E661" s="4" t="inlineStr">
         <is>
-          <t>Tier 1 producer · last check-in Jul 11</t>
+          <t>Tier 1 producer · tier Prospect→Tier 1 (Sep 22) · last check-in Sep 21</t>
         </is>
       </c>
       <c r="F661" s="3" t="inlineStr">
@@ -43536,17 +43532,17 @@
       </c>
       <c r="G661" s="3" t="inlineStr">
         <is>
-          <t>8c790bf8-a496-4f6f-9902-402d9161edf4</t>
+          <t>e88886fb-60ef-4d4e-8d44-578baf30fd25</t>
         </is>
       </c>
       <c r="H661" s="3" t="inlineStr">
         <is>
-          <t>PCP / IM / FM</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I661" s="3" t="inlineStr">
         <is>
-          <t>Added Sep 3 (Joe — referral receipts)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J661" s="3" t="n">
@@ -43554,12 +43550,12 @@
       </c>
       <c r="K661" s="3" t="inlineStr">
         <is>
-          <t>Southgate</t>
+          <t>Wyandotte</t>
         </is>
       </c>
       <c r="L661" s="4" t="inlineStr">
         <is>
-          <t>15450 Northline Road, Southgate, MI 48195</t>
+          <t>2300 Biddle Avenue, Wyandotte, Michigan, 48192</t>
         </is>
       </c>
       <c r="M661" s="4" t="n"/>
@@ -43573,53 +43569,53 @@
       </c>
       <c r="B662" s="3" t="inlineStr">
         <is>
-          <t>J-B01</t>
+          <t>J-A12</t>
         </is>
       </c>
       <c r="C662" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D662" s="4" t="inlineStr">
+        <is>
+          <t>Epic Medical Center</t>
+        </is>
+      </c>
+      <c r="E662" s="4" t="inlineStr">
+        <is>
+          <t>Tier 1 producer · last check-in Jul 11</t>
+        </is>
+      </c>
+      <c r="F662" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G662" s="3" t="inlineStr">
+        <is>
+          <t>8c790bf8-a496-4f6f-9902-402d9161edf4</t>
+        </is>
+      </c>
+      <c r="H662" s="3" t="inlineStr">
+        <is>
+          <t>PCP / IM / FM</t>
+        </is>
+      </c>
+      <c r="I662" s="3" t="inlineStr">
+        <is>
+          <t>Added Sep 3 (Joe — referral receipts)</t>
+        </is>
+      </c>
+      <c r="J662" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D662" s="4" t="inlineStr">
-        <is>
-          <t>📝 Park Family Practice - Novi</t>
-        </is>
-      </c>
-      <c r="E662" s="4" t="inlineStr">
-        <is>
-          <t>Tier 3 · last check-in Oct 7</t>
-        </is>
-      </c>
-      <c r="F662" s="3" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
-        </is>
-      </c>
-      <c r="G662" s="3" t="inlineStr">
-        <is>
-          <t>210797fc-d818-410f-94de-02c502935d29</t>
-        </is>
-      </c>
-      <c r="H662" s="3" t="inlineStr">
-        <is>
-          <t>PCP</t>
-        </is>
-      </c>
-      <c r="I662" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J662" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>Novi</t>
+          <t>Southgate</t>
         </is>
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>26850 PROVIDENCE PKWY STE 370, NOVI, MI, 48374</t>
+          <t>15450 Northline Road, Southgate, MI 48195</t>
         </is>
       </c>
       <c r="M662" s="4" t="n"/>
@@ -43637,31 +43633,31 @@
         </is>
       </c>
       <c r="C663" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D663" s="4" t="inlineStr">
         <is>
-          <t>📝 Village Medical - Novi</t>
+          <t>📝 Park Family Practice - Novi</t>
         </is>
       </c>
       <c r="E663" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Sep 29</t>
+          <t>Tier 3 · last check-in Oct 7</t>
         </is>
       </c>
       <c r="F663" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G663" s="3" t="inlineStr">
         <is>
-          <t>60ca59a0-452f-4fea-8aff-cf4ef63862b7</t>
+          <t>210797fc-d818-410f-94de-02c502935d29</t>
         </is>
       </c>
       <c r="H663" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I663" s="3" t="inlineStr">
@@ -43679,7 +43675,7 @@
       </c>
       <c r="L663" s="4" t="inlineStr">
         <is>
-          <t>39475 Lewis Dr ste 130, Novi, Michigan, 48377</t>
+          <t>26850 PROVIDENCE PKWY STE 370, NOVI, MI, 48374</t>
         </is>
       </c>
       <c r="M663" s="4" t="n"/>
@@ -43697,16 +43693,16 @@
         </is>
       </c>
       <c r="C664" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D664" s="4" t="inlineStr">
         <is>
-          <t>📝 ASCENSION MEDICAL GROUP WEST BLOOMFIELD FAMILY PRACTICE</t>
+          <t>📝 Village Medical - Novi</t>
         </is>
       </c>
       <c r="E664" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Sep 29</t>
+          <t>Tier 2 ortho · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F664" s="3" t="inlineStr">
@@ -43716,12 +43712,12 @@
       </c>
       <c r="G664" s="3" t="inlineStr">
         <is>
-          <t>611f52cc-838d-405e-8988-68708f39608e</t>
+          <t>60ca59a0-452f-4fea-8aff-cf4ef63862b7</t>
         </is>
       </c>
       <c r="H664" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="I664" s="3" t="inlineStr">
@@ -43739,7 +43735,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>28455 HAGGERTY RD STE 100, NOVI, MI, 48377</t>
+          <t>39475 Lewis Dr ste 130, Novi, Michigan, 48377</t>
         </is>
       </c>
       <c r="M664" s="4" t="n"/>
@@ -43757,16 +43753,16 @@
         </is>
       </c>
       <c r="C665" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D665" s="4" t="inlineStr">
         <is>
-          <t>📝 IHA Plymouth Primary Care</t>
+          <t>📝 ASCENSION MEDICAL GROUP WEST BLOOMFIELD FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="E665" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Oct 2</t>
+          <t>Tier 2 ortho · tier Tier 3→Tier 2 (Sep 22) · last check-in Sep 29</t>
         </is>
       </c>
       <c r="F665" s="3" t="inlineStr">
@@ -43776,7 +43772,7 @@
       </c>
       <c r="G665" s="3" t="inlineStr">
         <is>
-          <t>92cc3682-defe-42ff-8ccd-0ff138c12b77</t>
+          <t>611f52cc-838d-405e-8988-68708f39608e</t>
         </is>
       </c>
       <c r="H665" s="3" t="inlineStr">
@@ -43794,12 +43790,12 @@
       </c>
       <c r="K665" s="3" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Novi</t>
         </is>
       </c>
       <c r="L665" s="4" t="inlineStr">
         <is>
-          <t>990 w Ann Arbor trail, ste 208, PLYMOUTH, Michigan, 48170</t>
+          <t>28455 HAGGERTY RD STE 100, NOVI, MI, 48377</t>
         </is>
       </c>
       <c r="M665" s="4" t="n"/>
@@ -43817,11 +43813,11 @@
         </is>
       </c>
       <c r="C666" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D666" s="4" t="inlineStr">
         <is>
-          <t>📝 Office of Jeff The DO</t>
+          <t>📝 IHA Plymouth Primary Care</t>
         </is>
       </c>
       <c r="E666" s="4" t="inlineStr">
@@ -43836,7 +43832,7 @@
       </c>
       <c r="G666" s="3" t="inlineStr">
         <is>
-          <t>1710940242</t>
+          <t>92cc3682-defe-42ff-8ccd-0ff138c12b77</t>
         </is>
       </c>
       <c r="H666" s="3" t="inlineStr">
@@ -43859,7 +43855,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>990 West Ann Arbor Trail, Plymouth, Michigan, 48170</t>
+          <t>990 w Ann Arbor trail, ste 208, PLYMOUTH, Michigan, 48170</t>
         </is>
       </c>
       <c r="M666" s="4" t="n"/>
@@ -43877,31 +43873,31 @@
         </is>
       </c>
       <c r="C667" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D667" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Urgent Care-Canton</t>
+          <t>📝 Office of Jeff The DO</t>
         </is>
       </c>
       <c r="E667" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 23</t>
+          <t>Tier 2 ortho · last check-in Oct 2</t>
         </is>
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G667" s="3" t="inlineStr">
         <is>
-          <t>ad812b91-cf8d-48ca-b32b-6a2501ba9e67</t>
+          <t>1710940242</t>
         </is>
       </c>
       <c r="H667" s="3" t="inlineStr">
         <is>
-          <t>Urgent care</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I667" s="3" t="inlineStr">
@@ -43914,12 +43910,12 @@
       </c>
       <c r="K667" s="3" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="L667" s="4" t="inlineStr">
         <is>
-          <t>6549 N Canton Center Rd, Michigan, 48187</t>
+          <t>990 West Ann Arbor Trail, Plymouth, Michigan, 48170</t>
         </is>
       </c>
       <c r="M667" s="4" t="n"/>
@@ -43937,31 +43933,31 @@
         </is>
       </c>
       <c r="C668" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D668" s="4" t="inlineStr">
         <is>
-          <t>📝 CoreWell Health Family Medicine</t>
+          <t>Corewell Health Urgent Care-Canton</t>
         </is>
       </c>
       <c r="E668" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · last check-in Oct 1</t>
+          <t>Prospect · last check-in Jul 23</t>
         </is>
       </c>
       <c r="F668" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G668" s="3" t="inlineStr">
         <is>
-          <t>f8c5f64c-4cf6-463f-9090-68ac9735f08e</t>
+          <t>ad812b91-cf8d-48ca-b32b-6a2501ba9e67</t>
         </is>
       </c>
       <c r="H668" s="3" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>Urgent care</t>
         </is>
       </c>
       <c r="I668" s="3" t="inlineStr">
@@ -43979,7 +43975,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2050 N Haggerty Road, Canton, Michigan, 48187</t>
+          <t>6549 N Canton Center Rd, Michigan, 48187</t>
         </is>
       </c>
       <c r="M668" s="4" t="n"/>
@@ -43997,26 +43993,26 @@
         </is>
       </c>
       <c r="C669" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D669" s="4" t="inlineStr">
         <is>
-          <t>Advanced Primary Care</t>
+          <t>📝 CoreWell Health Family Medicine</t>
         </is>
       </c>
       <c r="E669" s="4" t="inlineStr">
         <is>
-          <t>Prospect · last check-in Jul 23</t>
+          <t>Tier 2 ortho · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F669" s="3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G669" s="3" t="inlineStr">
         <is>
-          <t>6101ca46-69b5-43a2-a4cd-74be14995963</t>
+          <t>f8c5f64c-4cf6-463f-9090-68ac9735f08e</t>
         </is>
       </c>
       <c r="H669" s="3" t="inlineStr">
@@ -44039,7 +44035,7 @@
       </c>
       <c r="L669" s="4" t="inlineStr">
         <is>
-          <t>43050 Ford Road, suite 170, CANTON, Michigan, 48187</t>
+          <t>2050 N Haggerty Road, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M669" s="4" t="n"/>
@@ -44057,26 +44053,26 @@
         </is>
       </c>
       <c r="C670" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D670" s="4" t="inlineStr">
         <is>
-          <t>📝 Partners in Internal Medicine</t>
+          <t>Advanced Primary Care</t>
         </is>
       </c>
       <c r="E670" s="4" t="inlineStr">
         <is>
-          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Oct 1</t>
+          <t>Prospect · last check-in Jul 23</t>
         </is>
       </c>
       <c r="F670" s="3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="G670" s="3" t="inlineStr">
         <is>
-          <t>2bc5b4b8-9395-4f0a-bc36-8f7ffd755481</t>
+          <t>6101ca46-69b5-43a2-a4cd-74be14995963</t>
         </is>
       </c>
       <c r="H670" s="3" t="inlineStr">
@@ -44099,7 +44095,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>255 N Lilley Rd, Canton, Michigan, 48187</t>
+          <t>43050 Ford Road, suite 170, CANTON, Michigan, 48187</t>
         </is>
       </c>
       <c r="M670" s="4" t="n"/>
@@ -44117,31 +44113,31 @@
         </is>
       </c>
       <c r="C671" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D671" s="4" t="inlineStr">
         <is>
-          <t>📝 Trinity URGENT CARE CANTON</t>
+          <t>📝 Partners in Internal Medicine</t>
         </is>
       </c>
       <c r="E671" s="4" t="inlineStr">
         <is>
-          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Oct 2</t>
+          <t>Tier 2 ortho · tier Prospect→Tier 2 (Sep 22) · last check-in Oct 1</t>
         </is>
       </c>
       <c r="F671" s="3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G671" s="3" t="inlineStr">
         <is>
-          <t>c78e3b81-c68a-4687-a4e9-a88863c2c873</t>
+          <t>2bc5b4b8-9395-4f0a-bc36-8f7ffd755481</t>
         </is>
       </c>
       <c r="H671" s="3" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="I671" s="3" t="inlineStr">
@@ -44159,11 +44155,71 @@
       </c>
       <c r="L671" s="4" t="inlineStr">
         <is>
-          <t>1600 S Canton Center Road, Canton, Michigan, 48188</t>
+          <t>255 N Lilley Rd, Canton, Michigan, 48187</t>
         </is>
       </c>
       <c r="M671" s="4" t="n"/>
       <c r="N671" s="3" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="3" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>J-B01</t>
+        </is>
+      </c>
+      <c r="C672" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D672" s="4" t="inlineStr">
+        <is>
+          <t>📝 Trinity URGENT CARE CANTON</t>
+        </is>
+      </c>
+      <c r="E672" s="4" t="inlineStr">
+        <is>
+          <t>Tier 3 · tier Prospect→Tier 3 (Sep 22) · last check-in Oct 2</t>
+        </is>
+      </c>
+      <c r="F672" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G672" s="3" t="inlineStr">
+        <is>
+          <t>c78e3b81-c68a-4687-a4e9-a88863c2c873</t>
+        </is>
+      </c>
+      <c r="H672" s="3" t="inlineStr">
+        <is>
+          <t>Orthopedic</t>
+        </is>
+      </c>
+      <c r="I672" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J672" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K672" s="3" t="inlineStr">
+        <is>
+          <t>Canton</t>
+        </is>
+      </c>
+      <c r="L672" s="4" t="inlineStr">
+        <is>
+          <t>1600 S Canton Center Road, Canton, Michigan, 48188</t>
+        </is>
+      </c>
+      <c r="M672" s="4" t="n"/>
+      <c r="N672" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -65206,7 +65262,7 @@
         <v>50</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>10</v>
@@ -65215,7 +65271,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -65231,7 +65287,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>22</v>
@@ -65240,7 +65296,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -65278,7 +65334,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>7</v>
@@ -65290,7 +65346,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
